--- a/FP.xlsx
+++ b/FP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD4D73A-7C27-4233-B8A4-9EB2C3B0F7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41426294-6545-418F-89AA-BF24C9B252F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Men!$A$1:$Q$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Women!$A$1:$Q$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -12458,34 +12459,34 @@
         <v>15</v>
       </c>
       <c r="F6" s="8">
-        <v>177.5</v>
+        <v>200</v>
       </c>
       <c r="G6" s="8">
-        <v>182.5</v>
+        <v>215</v>
       </c>
       <c r="H6" s="8">
-        <v>187.5</v>
+        <v>222.5</v>
       </c>
       <c r="I6" s="8">
-        <v>232.5</v>
+        <v>240</v>
       </c>
       <c r="J6" s="8">
-        <v>237.5</v>
+        <v>250</v>
       </c>
       <c r="K6" s="8">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="L6" s="8">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="M6" s="8">
-        <v>322.5</v>
+        <v>342.5</v>
       </c>
       <c r="N6" s="8">
-        <v>332.5</v>
+        <v>355</v>
       </c>
       <c r="O6" s="8">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="P6" s="8">
         <v>380</v>
@@ -20710,6 +20711,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q1" xr:uid="{E3552810-31BB-4B88-9769-989F9422D843}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/FP.xlsx
+++ b/FP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamr\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgsafety-my.sharepoint.com/personal/adam_riman_mgsafety_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41426294-6545-418F-89AA-BF24C9B252F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{41426294-6545-418F-89AA-BF24C9B252F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2A6F668-C180-4202-9141-FFA0CF9113AC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Men" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Men!$A$1:$Q$321</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Women!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Women!$A$1:$Q$161</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="27">
   <si>
     <t>140+</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>110+</t>
+  </si>
+  <si>
+    <t>70-79</t>
   </si>
 </sst>
 </file>
@@ -573,18 +576,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q321"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q341"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -637,7 +640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -690,7 +693,7 @@
         <v>502.5</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -743,7 +746,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -796,7 +799,7 @@
         <v>557.5</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -849,7 +852,7 @@
         <v>652.5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -902,7 +905,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -955,7 +958,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1008,7 +1011,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1061,7 +1064,7 @@
         <v>547.5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1114,7 +1117,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -1167,7 +1170,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -1220,7 +1223,7 @@
         <v>637.5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -1273,7 +1276,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1326,7 +1329,7 @@
         <v>877.5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -1379,7 +1382,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -1432,7 +1435,7 @@
         <v>692.5</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -1538,7 +1541,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -1591,7 +1594,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -1644,7 +1647,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
@@ -1697,7 +1700,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -1803,7 +1806,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
@@ -1856,7 +1859,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -1909,7 +1912,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
@@ -1962,7 +1965,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
@@ -2015,7 +2018,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
@@ -2068,7 +2071,7 @@
         <v>232.5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
@@ -2121,7 +2124,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -2174,7 +2177,7 @@
         <v>317.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -2227,7 +2230,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
@@ -2280,7 +2283,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -2333,7 +2336,7 @@
         <v>227.5</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
@@ -2386,7 +2389,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
@@ -2439,7 +2442,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>7</v>
       </c>
@@ -2492,7 +2495,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
@@ -2545,7 +2548,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>9</v>
       </c>
@@ -2598,7 +2601,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -2651,7 +2654,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -2704,7 +2707,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -2757,7 +2760,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>5</v>
       </c>
@@ -2810,7 +2813,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
@@ -2863,7 +2866,7 @@
         <v>232.5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -2916,7 +2919,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>8</v>
       </c>
@@ -2969,7 +2972,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
@@ -3022,7 +3025,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -3075,7 +3078,7 @@
         <v>312.5</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
@@ -3128,7 +3131,7 @@
         <v>282.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -3181,7 +3184,7 @@
         <v>252.5</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>5</v>
       </c>
@@ -3234,7 +3237,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
@@ -3287,7 +3290,7 @@
         <v>472.5</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
@@ -3340,7 +3343,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>8</v>
       </c>
@@ -3393,7 +3396,7 @@
         <v>582.5</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>9</v>
       </c>
@@ -3446,7 +3449,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -3499,7 +3502,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
@@ -3552,7 +3555,7 @@
         <v>542.5</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -3605,7 +3608,7 @@
         <v>487.5</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>5</v>
       </c>
@@ -3658,7 +3661,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
@@ -3711,7 +3714,7 @@
         <v>522.5</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>7</v>
       </c>
@@ -3764,7 +3767,7 @@
         <v>577.5</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>8</v>
       </c>
@@ -3817,7 +3820,7 @@
         <v>677.5</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>9</v>
       </c>
@@ -3870,7 +3873,7 @@
         <v>797.5</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>10</v>
       </c>
@@ -3923,7 +3926,7 @@
         <v>697.5</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
@@ -3976,7 +3979,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -4029,7 +4032,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>5</v>
       </c>
@@ -4082,7 +4085,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
@@ -4135,7 +4138,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>7</v>
       </c>
@@ -4188,7 +4191,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>8</v>
       </c>
@@ -4241,7 +4244,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>9</v>
       </c>
@@ -4294,7 +4297,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>10</v>
       </c>
@@ -4347,7 +4350,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -4400,7 +4403,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -4453,7 +4456,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>5</v>
       </c>
@@ -4506,7 +4509,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
@@ -4559,7 +4562,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>7</v>
       </c>
@@ -4612,7 +4615,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>8</v>
       </c>
@@ -4665,7 +4668,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>9</v>
       </c>
@@ -4718,7 +4721,7 @@
         <v>287.5</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>10</v>
       </c>
@@ -4771,7 +4774,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -4824,7 +4827,7 @@
         <v>227.5</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -4877,7 +4880,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>5</v>
       </c>
@@ -4930,7 +4933,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>6</v>
       </c>
@@ -4983,7 +4986,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>7</v>
       </c>
@@ -5036,7 +5039,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>8</v>
       </c>
@@ -5089,7 +5092,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
@@ -5142,7 +5145,7 @@
         <v>182.5</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>10</v>
       </c>
@@ -5195,7 +5198,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -5248,7 +5251,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>12</v>
       </c>
@@ -5301,7 +5304,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>5</v>
       </c>
@@ -5354,7 +5357,7 @@
         <v>202.5</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>6</v>
       </c>
@@ -5407,7 +5410,7 @@
         <v>222.5</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>7</v>
       </c>
@@ -5460,7 +5463,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>8</v>
       </c>
@@ -5513,7 +5516,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>9</v>
       </c>
@@ -5566,7 +5569,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>10</v>
       </c>
@@ -5619,7 +5622,7 @@
         <v>297.5</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>11</v>
       </c>
@@ -5672,7 +5675,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>12</v>
       </c>
@@ -5725,7 +5728,7 @@
         <v>242.5</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>5</v>
       </c>
@@ -5778,7 +5781,7 @@
         <v>492.5</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>6</v>
       </c>
@@ -5831,7 +5834,7 @@
         <v>517.5</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>7</v>
       </c>
@@ -5884,7 +5887,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>8</v>
       </c>
@@ -5937,7 +5940,7 @@
         <v>637.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>9</v>
       </c>
@@ -5990,7 +5993,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
@@ -6043,7 +6046,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
@@ -6096,7 +6099,7 @@
         <v>592.5</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>12</v>
       </c>
@@ -6149,7 +6152,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>5</v>
       </c>
@@ -6202,7 +6205,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>6</v>
       </c>
@@ -6255,7 +6258,7 @@
         <v>567.5</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>7</v>
       </c>
@@ -6308,7 +6311,7 @@
         <v>627.5</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>8</v>
       </c>
@@ -6361,7 +6364,7 @@
         <v>732.5</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>9</v>
       </c>
@@ -6414,7 +6417,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>10</v>
       </c>
@@ -6467,7 +6470,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -6520,7 +6523,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>12</v>
       </c>
@@ -6573,7 +6576,7 @@
         <v>617.5</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>5</v>
       </c>
@@ -6626,7 +6629,7 @@
         <v>102.5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>6</v>
       </c>
@@ -6679,7 +6682,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>7</v>
       </c>
@@ -6732,7 +6735,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>8</v>
       </c>
@@ -6785,7 +6788,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>9</v>
       </c>
@@ -6838,7 +6841,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>10</v>
       </c>
@@ -6891,7 +6894,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>11</v>
       </c>
@@ -6944,7 +6947,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>12</v>
       </c>
@@ -6997,7 +7000,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>5</v>
       </c>
@@ -7050,7 +7053,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>6</v>
       </c>
@@ -7103,7 +7106,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>7</v>
       </c>
@@ -7156,7 +7159,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>8</v>
       </c>
@@ -7209,7 +7212,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
@@ -7262,7 +7265,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -7315,7 +7318,7 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>11</v>
       </c>
@@ -7368,7 +7371,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>12</v>
       </c>
@@ -7421,7 +7424,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>5</v>
       </c>
@@ -7474,7 +7477,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>6</v>
       </c>
@@ -7527,7 +7530,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>7</v>
       </c>
@@ -7580,7 +7583,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>8</v>
       </c>
@@ -7633,7 +7636,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
@@ -7686,7 +7689,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>10</v>
       </c>
@@ -7739,7 +7742,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>11</v>
       </c>
@@ -7792,7 +7795,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>12</v>
       </c>
@@ -7845,7 +7848,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>5</v>
       </c>
@@ -7898,7 +7901,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>6</v>
       </c>
@@ -7951,7 +7954,7 @@
         <v>222.5</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>7</v>
       </c>
@@ -8004,7 +8007,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>8</v>
       </c>
@@ -8057,7 +8060,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -8110,7 +8113,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
@@ -8163,7 +8166,7 @@
         <v>297.5</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>11</v>
       </c>
@@ -8216,7 +8219,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>12</v>
       </c>
@@ -8269,7 +8272,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>5</v>
       </c>
@@ -8322,7 +8325,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>6</v>
       </c>
@@ -8375,7 +8378,7 @@
         <v>502.5</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>7</v>
       </c>
@@ -8428,7 +8431,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>8</v>
       </c>
@@ -8481,7 +8484,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>9</v>
       </c>
@@ -8534,7 +8537,7 @@
         <v>727.5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>10</v>
       </c>
@@ -8587,7 +8590,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -8640,7 +8643,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>12</v>
       </c>
@@ -8693,7 +8696,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>5</v>
       </c>
@@ -8746,7 +8749,7 @@
         <v>492.5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>6</v>
       </c>
@@ -8799,7 +8802,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>7</v>
       </c>
@@ -8852,7 +8855,7 @@
         <v>607.5</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>8</v>
       </c>
@@ -8905,7 +8908,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>9</v>
       </c>
@@ -8958,7 +8961,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -9011,7 +9014,7 @@
         <v>732.5</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>11</v>
       </c>
@@ -9064,7 +9067,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>12</v>
       </c>
@@ -9117,7 +9120,7 @@
         <v>597.5</v>
       </c>
     </row>
-    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -9136,7 +9139,7 @@
       <c r="P162" s="3"/>
       <c r="Q162" s="3"/>
     </row>
-    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -9155,7 +9158,7 @@
       <c r="P163" s="3"/>
       <c r="Q163" s="3"/>
     </row>
-    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -9174,7 +9177,7 @@
       <c r="P164" s="3"/>
       <c r="Q164" s="3"/>
     </row>
-    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -9193,7 +9196,7 @@
       <c r="P165" s="3"/>
       <c r="Q165" s="3"/>
     </row>
-    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -9212,7 +9215,7 @@
       <c r="P166" s="3"/>
       <c r="Q166" s="3"/>
     </row>
-    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -9231,7 +9234,7 @@
       <c r="P167" s="3"/>
       <c r="Q167" s="3"/>
     </row>
-    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -9250,7 +9253,7 @@
       <c r="P168" s="3"/>
       <c r="Q168" s="3"/>
     </row>
-    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -9269,7 +9272,7 @@
       <c r="P169" s="3"/>
       <c r="Q169" s="3"/>
     </row>
-    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -9288,7 +9291,7 @@
       <c r="P170" s="3"/>
       <c r="Q170" s="3"/>
     </row>
-    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -9307,7 +9310,7 @@
       <c r="P171" s="3"/>
       <c r="Q171" s="3"/>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -9326,7 +9329,7 @@
       <c r="P172" s="3"/>
       <c r="Q172" s="3"/>
     </row>
-    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -9345,7 +9348,7 @@
       <c r="P173" s="3"/>
       <c r="Q173" s="3"/>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -9364,7 +9367,7 @@
       <c r="P174" s="3"/>
       <c r="Q174" s="3"/>
     </row>
-    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -9383,7 +9386,7 @@
       <c r="P175" s="3"/>
       <c r="Q175" s="3"/>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -9402,7 +9405,7 @@
       <c r="P176" s="3"/>
       <c r="Q176" s="3"/>
     </row>
-    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -9421,7 +9424,7 @@
       <c r="P177" s="3"/>
       <c r="Q177" s="3"/>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -9440,7 +9443,7 @@
       <c r="P178" s="3"/>
       <c r="Q178" s="3"/>
     </row>
-    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -9459,7 +9462,7 @@
       <c r="P179" s="3"/>
       <c r="Q179" s="3"/>
     </row>
-    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -9478,7 +9481,7 @@
       <c r="P180" s="3"/>
       <c r="Q180" s="3"/>
     </row>
-    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -9497,7 +9500,7 @@
       <c r="P181" s="3"/>
       <c r="Q181" s="3"/>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -9516,7 +9519,7 @@
       <c r="P182" s="3"/>
       <c r="Q182" s="3"/>
     </row>
-    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -9535,7 +9538,7 @@
       <c r="P183" s="3"/>
       <c r="Q183" s="3"/>
     </row>
-    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -9554,7 +9557,7 @@
       <c r="P184" s="3"/>
       <c r="Q184" s="3"/>
     </row>
-    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -9573,7 +9576,7 @@
       <c r="P185" s="3"/>
       <c r="Q185" s="3"/>
     </row>
-    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -9592,7 +9595,7 @@
       <c r="P186" s="3"/>
       <c r="Q186" s="3"/>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -9611,7 +9614,7 @@
       <c r="P187" s="3"/>
       <c r="Q187" s="3"/>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -9630,7 +9633,7 @@
       <c r="P188" s="3"/>
       <c r="Q188" s="3"/>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -9649,7 +9652,7 @@
       <c r="P189" s="3"/>
       <c r="Q189" s="3"/>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -9668,7 +9671,7 @@
       <c r="P190" s="3"/>
       <c r="Q190" s="3"/>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -9687,7 +9690,7 @@
       <c r="P191" s="3"/>
       <c r="Q191" s="3"/>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -9706,7 +9709,7 @@
       <c r="P192" s="3"/>
       <c r="Q192" s="3"/>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -9725,7 +9728,7 @@
       <c r="P193" s="3"/>
       <c r="Q193" s="3"/>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -9744,7 +9747,7 @@
       <c r="P194" s="5"/>
       <c r="Q194" s="5"/>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -9763,7 +9766,7 @@
       <c r="P195" s="5"/>
       <c r="Q195" s="5"/>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -9782,7 +9785,7 @@
       <c r="P196" s="5"/>
       <c r="Q196" s="5"/>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -9801,7 +9804,7 @@
       <c r="P197" s="5"/>
       <c r="Q197" s="5"/>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -9820,7 +9823,7 @@
       <c r="P198" s="5"/>
       <c r="Q198" s="5"/>
     </row>
-    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -9839,7 +9842,7 @@
       <c r="P199" s="5"/>
       <c r="Q199" s="5"/>
     </row>
-    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -9858,7 +9861,7 @@
       <c r="P200" s="5"/>
       <c r="Q200" s="5"/>
     </row>
-    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -9877,7 +9880,7 @@
       <c r="P201" s="5"/>
       <c r="Q201" s="5"/>
     </row>
-    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -9896,7 +9899,7 @@
       <c r="P202" s="5"/>
       <c r="Q202" s="5"/>
     </row>
-    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -9915,7 +9918,7 @@
       <c r="P203" s="5"/>
       <c r="Q203" s="5"/>
     </row>
-    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -9934,7 +9937,7 @@
       <c r="P204" s="5"/>
       <c r="Q204" s="5"/>
     </row>
-    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -9953,7 +9956,7 @@
       <c r="P205" s="5"/>
       <c r="Q205" s="5"/>
     </row>
-    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -9972,7 +9975,7 @@
       <c r="P206" s="5"/>
       <c r="Q206" s="5"/>
     </row>
-    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -9991,7 +9994,7 @@
       <c r="P207" s="5"/>
       <c r="Q207" s="5"/>
     </row>
-    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -10010,7 +10013,7 @@
       <c r="P208" s="5"/>
       <c r="Q208" s="5"/>
     </row>
-    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -10029,7 +10032,7 @@
       <c r="P209" s="5"/>
       <c r="Q209" s="5"/>
     </row>
-    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -10048,7 +10051,7 @@
       <c r="P210" s="5"/>
       <c r="Q210" s="5"/>
     </row>
-    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -10067,7 +10070,7 @@
       <c r="P211" s="5"/>
       <c r="Q211" s="5"/>
     </row>
-    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -10086,7 +10089,7 @@
       <c r="P212" s="5"/>
       <c r="Q212" s="5"/>
     </row>
-    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -10105,7 +10108,7 @@
       <c r="P213" s="5"/>
       <c r="Q213" s="5"/>
     </row>
-    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -10124,7 +10127,7 @@
       <c r="P214" s="5"/>
       <c r="Q214" s="5"/>
     </row>
-    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -10143,7 +10146,7 @@
       <c r="P215" s="5"/>
       <c r="Q215" s="5"/>
     </row>
-    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -10162,7 +10165,7 @@
       <c r="P216" s="5"/>
       <c r="Q216" s="5"/>
     </row>
-    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -10181,7 +10184,7 @@
       <c r="P217" s="5"/>
       <c r="Q217" s="5"/>
     </row>
-    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -10200,7 +10203,7 @@
       <c r="P218" s="5"/>
       <c r="Q218" s="5"/>
     </row>
-    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -10219,7 +10222,7 @@
       <c r="P219" s="5"/>
       <c r="Q219" s="5"/>
     </row>
-    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -10238,7 +10241,7 @@
       <c r="P220" s="5"/>
       <c r="Q220" s="5"/>
     </row>
-    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -10257,7 +10260,7 @@
       <c r="P221" s="5"/>
       <c r="Q221" s="5"/>
     </row>
-    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -10276,7 +10279,7 @@
       <c r="P222" s="5"/>
       <c r="Q222" s="5"/>
     </row>
-    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -10295,7 +10298,7 @@
       <c r="P223" s="5"/>
       <c r="Q223" s="5"/>
     </row>
-    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -10314,7 +10317,7 @@
       <c r="P224" s="5"/>
       <c r="Q224" s="5"/>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -10333,7 +10336,7 @@
       <c r="P225" s="5"/>
       <c r="Q225" s="5"/>
     </row>
-    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -10352,7 +10355,7 @@
       <c r="P226" s="3"/>
       <c r="Q226" s="3"/>
     </row>
-    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -10371,7 +10374,7 @@
       <c r="P227" s="3"/>
       <c r="Q227" s="3"/>
     </row>
-    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -10390,7 +10393,7 @@
       <c r="P228" s="3"/>
       <c r="Q228" s="3"/>
     </row>
-    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -10409,7 +10412,7 @@
       <c r="P229" s="3"/>
       <c r="Q229" s="3"/>
     </row>
-    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -10428,7 +10431,7 @@
       <c r="P230" s="3"/>
       <c r="Q230" s="3"/>
     </row>
-    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -10447,7 +10450,7 @@
       <c r="P231" s="3"/>
       <c r="Q231" s="3"/>
     </row>
-    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -10466,7 +10469,7 @@
       <c r="P232" s="3"/>
       <c r="Q232" s="3"/>
     </row>
-    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -10485,7 +10488,7 @@
       <c r="P233" s="3"/>
       <c r="Q233" s="3"/>
     </row>
-    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -10504,7 +10507,7 @@
       <c r="P234" s="5"/>
       <c r="Q234" s="5"/>
     </row>
-    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -10523,7 +10526,7 @@
       <c r="P235" s="5"/>
       <c r="Q235" s="5"/>
     </row>
-    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -10542,7 +10545,7 @@
       <c r="P236" s="5"/>
       <c r="Q236" s="5"/>
     </row>
-    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -10561,7 +10564,7 @@
       <c r="P237" s="5"/>
       <c r="Q237" s="5"/>
     </row>
-    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -10580,7 +10583,7 @@
       <c r="P238" s="5"/>
       <c r="Q238" s="5"/>
     </row>
-    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -10599,7 +10602,7 @@
       <c r="P239" s="5"/>
       <c r="Q239" s="5"/>
     </row>
-    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -10618,7 +10621,7 @@
       <c r="P240" s="5"/>
       <c r="Q240" s="5"/>
     </row>
-    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -10637,7 +10640,7 @@
       <c r="P241" s="5"/>
       <c r="Q241" s="5"/>
     </row>
-    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -10656,7 +10659,7 @@
       <c r="P242" s="3"/>
       <c r="Q242" s="3"/>
     </row>
-    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -10675,7 +10678,7 @@
       <c r="P243" s="3"/>
       <c r="Q243" s="3"/>
     </row>
-    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -10694,7 +10697,7 @@
       <c r="P244" s="3"/>
       <c r="Q244" s="3"/>
     </row>
-    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -10713,7 +10716,7 @@
       <c r="P245" s="3"/>
       <c r="Q245" s="3"/>
     </row>
-    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -10732,7 +10735,7 @@
       <c r="P246" s="3"/>
       <c r="Q246" s="3"/>
     </row>
-    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -10751,7 +10754,7 @@
       <c r="P247" s="3"/>
       <c r="Q247" s="3"/>
     </row>
-    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -10770,7 +10773,7 @@
       <c r="P248" s="3"/>
       <c r="Q248" s="3"/>
     </row>
-    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -10789,7 +10792,7 @@
       <c r="P249" s="3"/>
       <c r="Q249" s="3"/>
     </row>
-    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -10808,7 +10811,7 @@
       <c r="P250" s="3"/>
       <c r="Q250" s="3"/>
     </row>
-    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -10827,7 +10830,7 @@
       <c r="P251" s="3"/>
       <c r="Q251" s="3"/>
     </row>
-    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -10846,7 +10849,7 @@
       <c r="P252" s="3"/>
       <c r="Q252" s="3"/>
     </row>
-    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -10865,7 +10868,7 @@
       <c r="P253" s="3"/>
       <c r="Q253" s="3"/>
     </row>
-    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -10884,7 +10887,7 @@
       <c r="P254" s="3"/>
       <c r="Q254" s="3"/>
     </row>
-    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -10903,7 +10906,7 @@
       <c r="P255" s="3"/>
       <c r="Q255" s="3"/>
     </row>
-    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -10922,7 +10925,7 @@
       <c r="P256" s="3"/>
       <c r="Q256" s="3"/>
     </row>
-    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -10941,7 +10944,7 @@
       <c r="P257" s="3"/>
       <c r="Q257" s="3"/>
     </row>
-    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -10960,7 +10963,7 @@
       <c r="P258" s="5"/>
       <c r="Q258" s="5"/>
     </row>
-    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -10979,7 +10982,7 @@
       <c r="P259" s="5"/>
       <c r="Q259" s="5"/>
     </row>
-    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -10998,7 +11001,7 @@
       <c r="P260" s="5"/>
       <c r="Q260" s="5"/>
     </row>
-    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -11017,7 +11020,7 @@
       <c r="P261" s="5"/>
       <c r="Q261" s="5"/>
     </row>
-    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -11036,7 +11039,7 @@
       <c r="P262" s="5"/>
       <c r="Q262" s="5"/>
     </row>
-    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -11055,7 +11058,7 @@
       <c r="P263" s="5"/>
       <c r="Q263" s="5"/>
     </row>
-    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -11074,7 +11077,7 @@
       <c r="P264" s="5"/>
       <c r="Q264" s="5"/>
     </row>
-    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -11093,7 +11096,7 @@
       <c r="P265" s="5"/>
       <c r="Q265" s="5"/>
     </row>
-    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -11112,7 +11115,7 @@
       <c r="P266" s="3"/>
       <c r="Q266" s="3"/>
     </row>
-    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -11131,7 +11134,7 @@
       <c r="P267" s="3"/>
       <c r="Q267" s="3"/>
     </row>
-    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -11150,7 +11153,7 @@
       <c r="P268" s="3"/>
       <c r="Q268" s="3"/>
     </row>
-    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -11169,7 +11172,7 @@
       <c r="P269" s="3"/>
       <c r="Q269" s="3"/>
     </row>
-    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -11188,7 +11191,7 @@
       <c r="P270" s="3"/>
       <c r="Q270" s="3"/>
     </row>
-    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -11207,7 +11210,7 @@
       <c r="P271" s="3"/>
       <c r="Q271" s="3"/>
     </row>
-    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -11226,7 +11229,7 @@
       <c r="P272" s="3"/>
       <c r="Q272" s="3"/>
     </row>
-    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -11245,7 +11248,7 @@
       <c r="P273" s="3"/>
       <c r="Q273" s="3"/>
     </row>
-    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -11264,7 +11267,7 @@
       <c r="P274" s="3"/>
       <c r="Q274" s="3"/>
     </row>
-    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -11283,7 +11286,7 @@
       <c r="P275" s="3"/>
       <c r="Q275" s="3"/>
     </row>
-    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -11302,7 +11305,7 @@
       <c r="P276" s="3"/>
       <c r="Q276" s="3"/>
     </row>
-    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -11321,7 +11324,7 @@
       <c r="P277" s="3"/>
       <c r="Q277" s="3"/>
     </row>
-    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -11340,7 +11343,7 @@
       <c r="P278" s="3"/>
       <c r="Q278" s="3"/>
     </row>
-    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -11359,7 +11362,7 @@
       <c r="P279" s="3"/>
       <c r="Q279" s="3"/>
     </row>
-    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -11378,7 +11381,7 @@
       <c r="P280" s="3"/>
       <c r="Q280" s="3"/>
     </row>
-    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -11397,7 +11400,7 @@
       <c r="P281" s="3"/>
       <c r="Q281" s="3"/>
     </row>
-    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -11416,7 +11419,7 @@
       <c r="P282" s="3"/>
       <c r="Q282" s="3"/>
     </row>
-    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -11435,7 +11438,7 @@
       <c r="P283" s="3"/>
       <c r="Q283" s="3"/>
     </row>
-    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -11454,7 +11457,7 @@
       <c r="P284" s="3"/>
       <c r="Q284" s="3"/>
     </row>
-    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -11473,7 +11476,7 @@
       <c r="P285" s="3"/>
       <c r="Q285" s="3"/>
     </row>
-    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -11492,7 +11495,7 @@
       <c r="P286" s="3"/>
       <c r="Q286" s="3"/>
     </row>
-    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -11511,7 +11514,7 @@
       <c r="P287" s="3"/>
       <c r="Q287" s="3"/>
     </row>
-    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -11530,7 +11533,7 @@
       <c r="P288" s="3"/>
       <c r="Q288" s="3"/>
     </row>
-    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -11549,7 +11552,7 @@
       <c r="P289" s="3"/>
       <c r="Q289" s="3"/>
     </row>
-    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -11568,7 +11571,7 @@
       <c r="P290" s="3"/>
       <c r="Q290" s="3"/>
     </row>
-    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -11587,7 +11590,7 @@
       <c r="P291" s="3"/>
       <c r="Q291" s="3"/>
     </row>
-    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -11606,7 +11609,7 @@
       <c r="P292" s="3"/>
       <c r="Q292" s="3"/>
     </row>
-    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -11625,7 +11628,7 @@
       <c r="P293" s="3"/>
       <c r="Q293" s="3"/>
     </row>
-    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -11644,7 +11647,7 @@
       <c r="P294" s="3"/>
       <c r="Q294" s="3"/>
     </row>
-    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -11663,7 +11666,7 @@
       <c r="P295" s="3"/>
       <c r="Q295" s="3"/>
     </row>
-    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -11682,7 +11685,7 @@
       <c r="P296" s="3"/>
       <c r="Q296" s="3"/>
     </row>
-    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -11701,7 +11704,7 @@
       <c r="P297" s="3"/>
       <c r="Q297" s="3"/>
     </row>
-    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -11720,7 +11723,7 @@
       <c r="P298" s="3"/>
       <c r="Q298" s="3"/>
     </row>
-    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -11739,7 +11742,7 @@
       <c r="P299" s="3"/>
       <c r="Q299" s="3"/>
     </row>
-    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -11758,7 +11761,7 @@
       <c r="P300" s="3"/>
       <c r="Q300" s="3"/>
     </row>
-    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -11777,7 +11780,7 @@
       <c r="P301" s="3"/>
       <c r="Q301" s="3"/>
     </row>
-    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -11796,7 +11799,7 @@
       <c r="P302" s="3"/>
       <c r="Q302" s="3"/>
     </row>
-    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -11815,7 +11818,7 @@
       <c r="P303" s="3"/>
       <c r="Q303" s="3"/>
     </row>
-    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -11834,7 +11837,7 @@
       <c r="P304" s="3"/>
       <c r="Q304" s="3"/>
     </row>
-    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -11853,7 +11856,7 @@
       <c r="P305" s="3"/>
       <c r="Q305" s="3"/>
     </row>
-    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -11872,7 +11875,7 @@
       <c r="P306" s="5"/>
       <c r="Q306" s="5"/>
     </row>
-    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -11891,7 +11894,7 @@
       <c r="P307" s="5"/>
       <c r="Q307" s="5"/>
     </row>
-    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -11910,7 +11913,7 @@
       <c r="P308" s="5"/>
       <c r="Q308" s="5"/>
     </row>
-    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -11929,7 +11932,7 @@
       <c r="P309" s="5"/>
       <c r="Q309" s="5"/>
     </row>
-    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -11948,7 +11951,7 @@
       <c r="P310" s="5"/>
       <c r="Q310" s="5"/>
     </row>
-    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -11967,7 +11970,7 @@
       <c r="P311" s="5"/>
       <c r="Q311" s="5"/>
     </row>
-    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -11986,7 +11989,7 @@
       <c r="P312" s="5"/>
       <c r="Q312" s="5"/>
     </row>
-    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -12005,7 +12008,7 @@
       <c r="P313" s="5"/>
       <c r="Q313" s="5"/>
     </row>
-    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -12024,7 +12027,7 @@
       <c r="P314" s="3"/>
       <c r="Q314" s="3"/>
     </row>
-    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -12043,7 +12046,7 @@
       <c r="P315" s="3"/>
       <c r="Q315" s="3"/>
     </row>
-    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -12062,7 +12065,7 @@
       <c r="P316" s="3"/>
       <c r="Q316" s="3"/>
     </row>
-    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -12081,7 +12084,7 @@
       <c r="P317" s="3"/>
       <c r="Q317" s="3"/>
     </row>
-    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -12100,7 +12103,7 @@
       <c r="P318" s="3"/>
       <c r="Q318" s="3"/>
     </row>
-    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -12119,7 +12122,7 @@
       <c r="P319" s="3"/>
       <c r="Q319" s="3"/>
     </row>
-    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -12138,7 +12141,7 @@
       <c r="P320" s="3"/>
       <c r="Q320" s="3"/>
     </row>
-    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -12157,8 +12160,1073 @@
       <c r="P321" s="3"/>
       <c r="Q321" s="3"/>
     </row>
+    <row r="322" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A322" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F322" s="1">
+        <v>182.5</v>
+      </c>
+      <c r="G322" s="1">
+        <v>245</v>
+      </c>
+      <c r="H322" s="1">
+        <v>337.5</v>
+      </c>
+      <c r="I322" s="1">
+        <v>362.5</v>
+      </c>
+      <c r="J322" s="1">
+        <v>397.5</v>
+      </c>
+      <c r="K322" s="1">
+        <v>415</v>
+      </c>
+      <c r="L322" s="1">
+        <v>427.5</v>
+      </c>
+      <c r="M322" s="1">
+        <v>442.5</v>
+      </c>
+      <c r="N322" s="1">
+        <v>460</v>
+      </c>
+      <c r="O322" s="1">
+        <v>472.5</v>
+      </c>
+      <c r="P322" s="1">
+        <v>482.5</v>
+      </c>
+      <c r="Q322" s="1">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="323" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A323" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E323" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F323" s="1">
+        <v>245</v>
+      </c>
+      <c r="G323" s="1">
+        <v>292.5</v>
+      </c>
+      <c r="H323" s="1">
+        <v>337.5</v>
+      </c>
+      <c r="I323" s="1">
+        <v>362.5</v>
+      </c>
+      <c r="J323" s="1">
+        <v>420</v>
+      </c>
+      <c r="K323" s="1">
+        <v>450</v>
+      </c>
+      <c r="L323" s="1">
+        <v>462.5</v>
+      </c>
+      <c r="M323" s="1">
+        <v>482.5</v>
+      </c>
+      <c r="N323" s="1">
+        <v>510</v>
+      </c>
+      <c r="O323" s="1">
+        <v>530</v>
+      </c>
+      <c r="P323" s="1">
+        <v>555</v>
+      </c>
+      <c r="Q323" s="1">
+        <v>562.5</v>
+      </c>
+    </row>
+    <row r="324" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A324" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F324" s="1">
+        <v>60</v>
+      </c>
+      <c r="G324" s="1">
+        <v>67.5</v>
+      </c>
+      <c r="H324" s="1">
+        <v>75</v>
+      </c>
+      <c r="I324" s="1">
+        <v>85</v>
+      </c>
+      <c r="J324" s="1">
+        <v>95</v>
+      </c>
+      <c r="K324" s="1">
+        <v>100</v>
+      </c>
+      <c r="L324" s="1">
+        <v>100</v>
+      </c>
+      <c r="M324" s="1">
+        <v>105</v>
+      </c>
+      <c r="N324" s="1">
+        <v>105</v>
+      </c>
+      <c r="O324" s="1">
+        <v>112.5</v>
+      </c>
+      <c r="P324" s="1">
+        <v>112.5</v>
+      </c>
+      <c r="Q324" s="1">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A325" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E325" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F325" s="1">
+        <v>110</v>
+      </c>
+      <c r="G325" s="1">
+        <v>117.5</v>
+      </c>
+      <c r="H325" s="1">
+        <v>130</v>
+      </c>
+      <c r="I325" s="1">
+        <v>150</v>
+      </c>
+      <c r="J325" s="1">
+        <v>165</v>
+      </c>
+      <c r="K325" s="1">
+        <v>177.5</v>
+      </c>
+      <c r="L325" s="1">
+        <v>180</v>
+      </c>
+      <c r="M325" s="1">
+        <v>185</v>
+      </c>
+      <c r="N325" s="1">
+        <v>192.5</v>
+      </c>
+      <c r="O325" s="1">
+        <v>197.5</v>
+      </c>
+      <c r="P325" s="1">
+        <v>202.5</v>
+      </c>
+      <c r="Q325" s="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="326" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A326" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F326" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="G326" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="H326" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="I326" s="1">
+        <v>82.5</v>
+      </c>
+      <c r="J326" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="K326" s="1">
+        <v>97.5</v>
+      </c>
+      <c r="L326" s="1">
+        <v>97.5</v>
+      </c>
+      <c r="M326" s="1">
+        <v>105</v>
+      </c>
+      <c r="N326" s="1">
+        <v>112.5</v>
+      </c>
+      <c r="O326" s="1">
+        <v>112.5</v>
+      </c>
+      <c r="P326" s="1">
+        <v>125</v>
+      </c>
+      <c r="Q326" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="327" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A327" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F327" s="1">
+        <v>90</v>
+      </c>
+      <c r="G327" s="1">
+        <v>100</v>
+      </c>
+      <c r="H327" s="1">
+        <v>112.5</v>
+      </c>
+      <c r="I327" s="1">
+        <v>137.5</v>
+      </c>
+      <c r="J327" s="1">
+        <v>150</v>
+      </c>
+      <c r="K327" s="1">
+        <v>170</v>
+      </c>
+      <c r="L327" s="1">
+        <v>180</v>
+      </c>
+      <c r="M327" s="1">
+        <v>185</v>
+      </c>
+      <c r="N327" s="1">
+        <v>192.5</v>
+      </c>
+      <c r="O327" s="1">
+        <v>205</v>
+      </c>
+      <c r="P327" s="1">
+        <v>225</v>
+      </c>
+      <c r="Q327" s="1">
+        <v>227.5</v>
+      </c>
+    </row>
+    <row r="328" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A328" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F328" s="1">
+        <v>222.5</v>
+      </c>
+      <c r="G328" s="1">
+        <v>252.5</v>
+      </c>
+      <c r="H328" s="1">
+        <v>280</v>
+      </c>
+      <c r="I328" s="1">
+        <v>320</v>
+      </c>
+      <c r="J328" s="1">
+        <v>355</v>
+      </c>
+      <c r="K328" s="1">
+        <v>377.5</v>
+      </c>
+      <c r="L328" s="1">
+        <v>385</v>
+      </c>
+      <c r="M328" s="1">
+        <v>397.5</v>
+      </c>
+      <c r="N328" s="1">
+        <v>407.5</v>
+      </c>
+      <c r="O328" s="1">
+        <v>420</v>
+      </c>
+      <c r="P328" s="1">
+        <v>430</v>
+      </c>
+      <c r="Q328" s="1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="329" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A329" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E329" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F329" s="1">
+        <v>180</v>
+      </c>
+      <c r="G329" s="1">
+        <v>202.5</v>
+      </c>
+      <c r="H329" s="1">
+        <v>235</v>
+      </c>
+      <c r="I329" s="1">
+        <v>290</v>
+      </c>
+      <c r="J329" s="1">
+        <v>332.5</v>
+      </c>
+      <c r="K329" s="1">
+        <v>375</v>
+      </c>
+      <c r="L329" s="1">
+        <v>392.5</v>
+      </c>
+      <c r="M329" s="1">
+        <v>407.5</v>
+      </c>
+      <c r="N329" s="1">
+        <v>430</v>
+      </c>
+      <c r="O329" s="1">
+        <v>450</v>
+      </c>
+      <c r="P329" s="1">
+        <v>497.5</v>
+      </c>
+      <c r="Q329" s="1">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="330" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A330" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F330" s="1">
+        <v>55</v>
+      </c>
+      <c r="G330" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="H330" s="1">
+        <v>67.5</v>
+      </c>
+      <c r="I330" s="1">
+        <v>77.5</v>
+      </c>
+      <c r="J330" s="1">
+        <v>85</v>
+      </c>
+      <c r="K330" s="1">
+        <v>90</v>
+      </c>
+      <c r="L330" s="1">
+        <v>90</v>
+      </c>
+      <c r="M330" s="1">
+        <v>95</v>
+      </c>
+      <c r="N330" s="1">
+        <v>95</v>
+      </c>
+      <c r="O330" s="1">
+        <v>100</v>
+      </c>
+      <c r="P330" s="1">
+        <v>105</v>
+      </c>
+      <c r="Q330" s="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="331" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A331" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E331" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F331" s="1">
+        <v>97.5</v>
+      </c>
+      <c r="G331" s="1">
+        <v>110</v>
+      </c>
+      <c r="H331" s="1">
+        <v>117.5</v>
+      </c>
+      <c r="I331" s="1">
+        <v>135</v>
+      </c>
+      <c r="J331" s="1">
+        <v>150</v>
+      </c>
+      <c r="K331" s="1">
+        <v>160</v>
+      </c>
+      <c r="L331" s="1">
+        <v>162.5</v>
+      </c>
+      <c r="M331" s="1">
+        <v>167.5</v>
+      </c>
+      <c r="N331" s="1">
+        <v>175</v>
+      </c>
+      <c r="O331" s="1">
+        <v>180</v>
+      </c>
+      <c r="P331" s="1">
+        <v>182.5</v>
+      </c>
+      <c r="Q331" s="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="332" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A332" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E332" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F332" s="1">
+        <v>45</v>
+      </c>
+      <c r="G332" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="H332" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="I332" s="1">
+        <v>67.5</v>
+      </c>
+      <c r="J332" s="1">
+        <v>80</v>
+      </c>
+      <c r="K332" s="1">
+        <v>90</v>
+      </c>
+      <c r="L332" s="1">
+        <v>92.5</v>
+      </c>
+      <c r="M332" s="1">
+        <v>95</v>
+      </c>
+      <c r="N332" s="1">
+        <v>105</v>
+      </c>
+      <c r="O332" s="1">
+        <v>107.5</v>
+      </c>
+      <c r="P332" s="1">
+        <v>115</v>
+      </c>
+      <c r="Q332" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="333" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A333" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F333" s="1">
+        <v>80</v>
+      </c>
+      <c r="G333" s="1">
+        <v>90</v>
+      </c>
+      <c r="H333" s="1">
+        <v>105</v>
+      </c>
+      <c r="I333" s="1">
+        <v>125</v>
+      </c>
+      <c r="J333" s="1">
+        <v>145</v>
+      </c>
+      <c r="K333" s="1">
+        <v>162.5</v>
+      </c>
+      <c r="L333" s="1">
+        <v>167.5</v>
+      </c>
+      <c r="M333" s="1">
+        <v>177.5</v>
+      </c>
+      <c r="N333" s="1">
+        <v>185</v>
+      </c>
+      <c r="O333" s="1">
+        <v>192.5</v>
+      </c>
+      <c r="P333" s="1">
+        <v>212.5</v>
+      </c>
+      <c r="Q333" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="334" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A334" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F334" s="1">
+        <v>180</v>
+      </c>
+      <c r="G334" s="1">
+        <v>240</v>
+      </c>
+      <c r="H334" s="1">
+        <v>332.5</v>
+      </c>
+      <c r="I334" s="1">
+        <v>357.5</v>
+      </c>
+      <c r="J334" s="1">
+        <v>387.5</v>
+      </c>
+      <c r="K334" s="1">
+        <v>405</v>
+      </c>
+      <c r="L334" s="1">
+        <v>417.5</v>
+      </c>
+      <c r="M334" s="1">
+        <v>432.5</v>
+      </c>
+      <c r="N334" s="1">
+        <v>447.5</v>
+      </c>
+      <c r="O334" s="1">
+        <v>460</v>
+      </c>
+      <c r="P334" s="1">
+        <v>472.5</v>
+      </c>
+      <c r="Q334" s="1">
+        <v>482.5</v>
+      </c>
+    </row>
+    <row r="335" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A335" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E335" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F335" s="1">
+        <v>227.5</v>
+      </c>
+      <c r="G335" s="1">
+        <v>275</v>
+      </c>
+      <c r="H335" s="1">
+        <v>315</v>
+      </c>
+      <c r="I335" s="1">
+        <v>357.5</v>
+      </c>
+      <c r="J335" s="1">
+        <v>412.5</v>
+      </c>
+      <c r="K335" s="1">
+        <v>442.5</v>
+      </c>
+      <c r="L335" s="1">
+        <v>452.5</v>
+      </c>
+      <c r="M335" s="1">
+        <v>475</v>
+      </c>
+      <c r="N335" s="1">
+        <v>500</v>
+      </c>
+      <c r="O335" s="1">
+        <v>520</v>
+      </c>
+      <c r="P335" s="1">
+        <v>535</v>
+      </c>
+      <c r="Q335" s="1">
+        <v>557.5</v>
+      </c>
+    </row>
+    <row r="336" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A336" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F336" s="1">
+        <v>57.5</v>
+      </c>
+      <c r="G336" s="1">
+        <v>67.5</v>
+      </c>
+      <c r="H336" s="1">
+        <v>72.5</v>
+      </c>
+      <c r="I336" s="1">
+        <v>82.5</v>
+      </c>
+      <c r="J336" s="1">
+        <v>90</v>
+      </c>
+      <c r="K336" s="1">
+        <v>95</v>
+      </c>
+      <c r="L336" s="1">
+        <v>95</v>
+      </c>
+      <c r="M336" s="1">
+        <v>100</v>
+      </c>
+      <c r="N336" s="1">
+        <v>100</v>
+      </c>
+      <c r="O336" s="1">
+        <v>107.5</v>
+      </c>
+      <c r="P336" s="1">
+        <v>110</v>
+      </c>
+      <c r="Q336" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="337" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A337" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E337" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F337" s="1">
+        <v>50</v>
+      </c>
+      <c r="G337" s="1">
+        <v>60</v>
+      </c>
+      <c r="H337" s="1">
+        <v>60</v>
+      </c>
+      <c r="I337" s="1">
+        <v>80</v>
+      </c>
+      <c r="J337" s="1">
+        <v>85</v>
+      </c>
+      <c r="K337" s="1">
+        <v>90</v>
+      </c>
+      <c r="L337" s="1">
+        <v>90</v>
+      </c>
+      <c r="M337" s="1">
+        <v>97.5</v>
+      </c>
+      <c r="N337" s="1">
+        <v>105</v>
+      </c>
+      <c r="O337" s="1">
+        <v>107.5</v>
+      </c>
+      <c r="P337" s="1">
+        <v>117.5</v>
+      </c>
+      <c r="Q337" s="1">
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="338" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A338" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E338" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F338" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="G338" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="H338" s="1">
+        <v>62.5</v>
+      </c>
+      <c r="I338" s="1">
+        <v>82.5</v>
+      </c>
+      <c r="J338" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="K338" s="1">
+        <v>95</v>
+      </c>
+      <c r="L338" s="1">
+        <v>95</v>
+      </c>
+      <c r="M338" s="1">
+        <v>102.5</v>
+      </c>
+      <c r="N338" s="1">
+        <v>110</v>
+      </c>
+      <c r="O338" s="1">
+        <v>112.5</v>
+      </c>
+      <c r="P338" s="1">
+        <v>122.5</v>
+      </c>
+      <c r="Q338" s="1">
+        <v>127.5</v>
+      </c>
+    </row>
+    <row r="339" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A339" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F339" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="G339" s="1">
+        <v>95</v>
+      </c>
+      <c r="H339" s="1">
+        <v>110</v>
+      </c>
+      <c r="I339" s="1">
+        <v>132.5</v>
+      </c>
+      <c r="J339" s="1">
+        <v>142.5</v>
+      </c>
+      <c r="K339" s="1">
+        <v>162.5</v>
+      </c>
+      <c r="L339" s="1">
+        <v>172.5</v>
+      </c>
+      <c r="M339" s="1">
+        <v>177.5</v>
+      </c>
+      <c r="N339" s="1">
+        <v>182.5</v>
+      </c>
+      <c r="O339" s="1">
+        <v>197.5</v>
+      </c>
+      <c r="P339" s="1">
+        <v>215</v>
+      </c>
+      <c r="Q339" s="1">
+        <v>217.5</v>
+      </c>
+    </row>
+    <row r="340" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A340" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F340" s="1">
+        <v>167.5</v>
+      </c>
+      <c r="G340" s="1">
+        <v>222.5</v>
+      </c>
+      <c r="H340" s="1">
+        <v>280</v>
+      </c>
+      <c r="I340" s="1">
+        <v>332.5</v>
+      </c>
+      <c r="J340" s="1">
+        <v>380</v>
+      </c>
+      <c r="K340" s="1">
+        <v>397.5</v>
+      </c>
+      <c r="L340" s="1">
+        <v>405</v>
+      </c>
+      <c r="M340" s="1">
+        <v>422.5</v>
+      </c>
+      <c r="N340" s="1">
+        <v>435</v>
+      </c>
+      <c r="O340" s="1">
+        <v>447.5</v>
+      </c>
+      <c r="P340" s="1">
+        <v>460</v>
+      </c>
+      <c r="Q340" s="1">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="341" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A341" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E341" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F341" s="1">
+        <v>222.5</v>
+      </c>
+      <c r="G341" s="1">
+        <v>267.5</v>
+      </c>
+      <c r="H341" s="1">
+        <v>305</v>
+      </c>
+      <c r="I341" s="1">
+        <v>345</v>
+      </c>
+      <c r="J341" s="1">
+        <v>400</v>
+      </c>
+      <c r="K341" s="1">
+        <v>427.5</v>
+      </c>
+      <c r="L341" s="1">
+        <v>440</v>
+      </c>
+      <c r="M341" s="1">
+        <v>460</v>
+      </c>
+      <c r="N341" s="1">
+        <v>485</v>
+      </c>
+      <c r="O341" s="1">
+        <v>505</v>
+      </c>
+      <c r="P341" s="1">
+        <v>517.5</v>
+      </c>
+      <c r="Q341" s="1">
+        <v>540</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q321" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="60-69"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="1">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12174,10 +13242,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3552810-31BB-4B88-9769-989F9422D843}">
-  <dimension ref="A1:Q161"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Q181"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -12230,7 +13302,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -12283,7 +13355,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -12336,7 +13408,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -12389,7 +13461,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -12442,7 +13514,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -12495,7 +13567,7 @@
         <v>397.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -12548,7 +13620,7 @@
         <v>347.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -12601,7 +13673,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -12654,7 +13726,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -12707,7 +13779,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -12760,7 +13832,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -12813,7 +13885,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -12866,7 +13938,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -12919,7 +13991,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -12972,7 +14044,7 @@
         <v>377.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -13025,7 +14097,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -13078,7 +14150,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -13131,7 +14203,7 @@
         <v>327.5</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -13184,7 +14256,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -13237,7 +14309,7 @@
         <v>362.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
@@ -13290,7 +14362,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -13343,7 +14415,7 @@
         <v>492.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -13396,7 +14468,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
@@ -13449,7 +14521,7 @@
         <v>392.5</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -13502,7 +14574,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
@@ -13555,7 +14627,7 @@
         <v>342.5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
@@ -13608,7 +14680,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
@@ -13661,7 +14733,7 @@
         <v>377.5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
@@ -13714,7 +14786,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -13767,7 +14839,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -13820,7 +14892,7 @@
         <v>452.5</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
@@ -13873,7 +14945,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -13926,7 +14998,7 @@
         <v>372.5</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
@@ -13979,7 +15051,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
@@ -14032,7 +15104,7 @@
         <v>262.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>7</v>
       </c>
@@ -14085,7 +15157,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
@@ -14138,7 +15210,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>9</v>
       </c>
@@ -14191,7 +15263,7 @@
         <v>422.5</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -14244,7 +15316,7 @@
         <v>347.5</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -14297,7 +15369,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -14350,7 +15422,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>5</v>
       </c>
@@ -14403,7 +15475,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
@@ -14456,7 +15528,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -14509,7 +15581,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>8</v>
       </c>
@@ -14562,7 +15634,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
@@ -14615,7 +15687,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -14668,7 +15740,7 @@
         <v>397.5</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
@@ -14721,7 +15793,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -14774,7 +15846,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>5</v>
       </c>
@@ -14827,7 +15899,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
@@ -14880,7 +15952,7 @@
         <v>297.5</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
@@ -14933,7 +16005,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>8</v>
       </c>
@@ -14986,7 +16058,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>9</v>
       </c>
@@ -15039,7 +16111,7 @@
         <v>452.5</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -15092,7 +16164,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
@@ -15145,7 +16217,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -15198,7 +16270,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>5</v>
       </c>
@@ -15251,7 +16323,7 @@
         <v>282.5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
@@ -15304,7 +16376,7 @@
         <v>312.5</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>7</v>
       </c>
@@ -15357,7 +16429,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>8</v>
       </c>
@@ -15410,7 +16482,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>9</v>
       </c>
@@ -15463,7 +16535,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>10</v>
       </c>
@@ -15516,7 +16588,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
@@ -15569,7 +16641,7 @@
         <v>377.5</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -15622,7 +16694,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>5</v>
       </c>
@@ -15675,7 +16747,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
@@ -15728,7 +16800,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>7</v>
       </c>
@@ -15781,7 +16853,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>8</v>
       </c>
@@ -15834,7 +16906,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>9</v>
       </c>
@@ -15887,7 +16959,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>10</v>
       </c>
@@ -15940,7 +17012,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -15993,7 +17065,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -16046,7 +17118,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>5</v>
       </c>
@@ -16099,7 +17171,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
@@ -16152,7 +17224,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>7</v>
       </c>
@@ -16205,7 +17277,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>8</v>
       </c>
@@ -16258,7 +17330,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>9</v>
       </c>
@@ -16311,7 +17383,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>10</v>
       </c>
@@ -16364,7 +17436,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -16417,7 +17489,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -16470,7 +17542,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>5</v>
       </c>
@@ -16523,7 +17595,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>6</v>
       </c>
@@ -16576,7 +17648,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>7</v>
       </c>
@@ -16629,7 +17701,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>8</v>
       </c>
@@ -16682,7 +17754,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
@@ -16735,7 +17807,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>10</v>
       </c>
@@ -16788,7 +17860,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -16841,7 +17913,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>12</v>
       </c>
@@ -16894,7 +17966,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>5</v>
       </c>
@@ -16947,7 +18019,7 @@
         <v>102.5</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>6</v>
       </c>
@@ -17000,7 +18072,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>7</v>
       </c>
@@ -17053,7 +18125,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>8</v>
       </c>
@@ -17106,7 +18178,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>9</v>
       </c>
@@ -17159,7 +18231,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>10</v>
       </c>
@@ -17212,7 +18284,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>11</v>
       </c>
@@ -17265,7 +18337,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>12</v>
       </c>
@@ -17318,7 +18390,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>5</v>
       </c>
@@ -17371,7 +18443,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>6</v>
       </c>
@@ -17424,7 +18496,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>7</v>
       </c>
@@ -17477,7 +18549,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>8</v>
       </c>
@@ -17530,7 +18602,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>9</v>
       </c>
@@ -17583,7 +18655,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
@@ -17636,7 +18708,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
@@ -17689,7 +18761,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>12</v>
       </c>
@@ -17742,7 +18814,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>5</v>
       </c>
@@ -17795,7 +18867,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>6</v>
       </c>
@@ -17848,7 +18920,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>7</v>
       </c>
@@ -17901,7 +18973,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>8</v>
       </c>
@@ -17954,7 +19026,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>9</v>
       </c>
@@ -18007,7 +19079,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>10</v>
       </c>
@@ -18060,7 +19132,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -18113,7 +19185,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>12</v>
       </c>
@@ -18166,7 +19238,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>5</v>
       </c>
@@ -18219,7 +19291,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>6</v>
       </c>
@@ -18272,7 +19344,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>7</v>
       </c>
@@ -18325,7 +19397,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>8</v>
       </c>
@@ -18378,7 +19450,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>9</v>
       </c>
@@ -18431,7 +19503,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>10</v>
       </c>
@@ -18484,7 +19556,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>11</v>
       </c>
@@ -18537,7 +19609,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>12</v>
       </c>
@@ -18590,7 +19662,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>5</v>
       </c>
@@ -18643,7 +19715,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>6</v>
       </c>
@@ -18696,7 +19768,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>7</v>
       </c>
@@ -18749,7 +19821,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>8</v>
       </c>
@@ -18802,7 +19874,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
@@ -18855,7 +19927,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -18908,7 +19980,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>11</v>
       </c>
@@ -18961,7 +20033,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>12</v>
       </c>
@@ -19014,7 +20086,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>5</v>
       </c>
@@ -19067,7 +20139,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>6</v>
       </c>
@@ -19120,7 +20192,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>7</v>
       </c>
@@ -19173,7 +20245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>8</v>
       </c>
@@ -19226,7 +20298,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
@@ -19279,7 +20351,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>10</v>
       </c>
@@ -19332,7 +20404,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>11</v>
       </c>
@@ -19385,7 +20457,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>12</v>
       </c>
@@ -19438,7 +20510,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>5</v>
       </c>
@@ -19491,7 +20563,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>6</v>
       </c>
@@ -19544,7 +20616,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>7</v>
       </c>
@@ -19597,7 +20669,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>8</v>
       </c>
@@ -19650,7 +20722,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -19703,7 +20775,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
@@ -19756,7 +20828,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>11</v>
       </c>
@@ -19809,7 +20881,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>12</v>
       </c>
@@ -19862,7 +20934,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>5</v>
       </c>
@@ -19915,7 +20987,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>6</v>
       </c>
@@ -19968,7 +21040,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>7</v>
       </c>
@@ -20021,7 +21093,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>8</v>
       </c>
@@ -20074,7 +21146,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>9</v>
       </c>
@@ -20127,7 +21199,7 @@
         <v>182.5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>10</v>
       </c>
@@ -20180,7 +21252,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -20233,7 +21305,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>12</v>
       </c>
@@ -20286,7 +21358,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>5</v>
       </c>
@@ -20339,7 +21411,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>6</v>
       </c>
@@ -20392,7 +21464,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>7</v>
       </c>
@@ -20445,7 +21517,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>8</v>
       </c>
@@ -20498,7 +21570,7 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>9</v>
       </c>
@@ -20551,7 +21623,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -20604,7 +21676,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>11</v>
       </c>
@@ -20657,7 +21729,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>12</v>
       </c>
@@ -20710,8 +21782,1074 @@
         <v>137.5</v>
       </c>
     </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F162">
+        <v>115</v>
+      </c>
+      <c r="G162">
+        <v>120</v>
+      </c>
+      <c r="H162">
+        <v>125</v>
+      </c>
+      <c r="I162">
+        <v>150</v>
+      </c>
+      <c r="J162">
+        <v>157.5</v>
+      </c>
+      <c r="K162">
+        <v>172.5</v>
+      </c>
+      <c r="L162">
+        <v>187.5</v>
+      </c>
+      <c r="M162">
+        <v>207.5</v>
+      </c>
+      <c r="N162">
+        <v>220</v>
+      </c>
+      <c r="O162">
+        <v>232.5</v>
+      </c>
+      <c r="P162">
+        <v>245</v>
+      </c>
+      <c r="Q162">
+        <v>257.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F163">
+        <v>122.5</v>
+      </c>
+      <c r="G163">
+        <v>127.5</v>
+      </c>
+      <c r="H163">
+        <v>132.5</v>
+      </c>
+      <c r="I163">
+        <v>180</v>
+      </c>
+      <c r="J163">
+        <v>202.5</v>
+      </c>
+      <c r="K163">
+        <v>217.5</v>
+      </c>
+      <c r="L163">
+        <v>225</v>
+      </c>
+      <c r="M163">
+        <v>237.5</v>
+      </c>
+      <c r="N163">
+        <v>247.5</v>
+      </c>
+      <c r="O163">
+        <v>260</v>
+      </c>
+      <c r="P163">
+        <v>270</v>
+      </c>
+      <c r="Q163">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F164">
+        <v>142.5</v>
+      </c>
+      <c r="G164">
+        <v>147.5</v>
+      </c>
+      <c r="H164">
+        <v>152.5</v>
+      </c>
+      <c r="I164">
+        <v>207.5</v>
+      </c>
+      <c r="J164">
+        <v>237.5</v>
+      </c>
+      <c r="K164">
+        <v>252.5</v>
+      </c>
+      <c r="L164">
+        <v>260</v>
+      </c>
+      <c r="M164">
+        <v>272.5</v>
+      </c>
+      <c r="N164">
+        <v>287.5</v>
+      </c>
+      <c r="O164">
+        <v>297.5</v>
+      </c>
+      <c r="P164">
+        <v>310</v>
+      </c>
+      <c r="Q164">
+        <v>322.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F165">
+        <v>150</v>
+      </c>
+      <c r="G165">
+        <v>155</v>
+      </c>
+      <c r="H165">
+        <v>157.5</v>
+      </c>
+      <c r="I165">
+        <v>217.5</v>
+      </c>
+      <c r="J165">
+        <v>247.5</v>
+      </c>
+      <c r="K165">
+        <v>265</v>
+      </c>
+      <c r="L165">
+        <v>270</v>
+      </c>
+      <c r="M165">
+        <v>285</v>
+      </c>
+      <c r="N165">
+        <v>297.5</v>
+      </c>
+      <c r="O165">
+        <v>310</v>
+      </c>
+      <c r="P165">
+        <v>322.5</v>
+      </c>
+      <c r="Q165">
+        <v>337.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F166">
+        <v>115</v>
+      </c>
+      <c r="G166">
+        <v>120</v>
+      </c>
+      <c r="H166">
+        <v>125</v>
+      </c>
+      <c r="I166">
+        <v>150</v>
+      </c>
+      <c r="J166">
+        <v>157.5</v>
+      </c>
+      <c r="K166">
+        <v>172.5</v>
+      </c>
+      <c r="L166">
+        <v>187.5</v>
+      </c>
+      <c r="M166">
+        <v>207.5</v>
+      </c>
+      <c r="N166">
+        <v>220</v>
+      </c>
+      <c r="O166">
+        <v>232.5</v>
+      </c>
+      <c r="P166">
+        <v>245</v>
+      </c>
+      <c r="Q166">
+        <v>257.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F167">
+        <v>147.5</v>
+      </c>
+      <c r="G167">
+        <v>152.5</v>
+      </c>
+      <c r="H167">
+        <v>157.5</v>
+      </c>
+      <c r="I167">
+        <v>167.5</v>
+      </c>
+      <c r="J167">
+        <v>195</v>
+      </c>
+      <c r="K167">
+        <v>222.5</v>
+      </c>
+      <c r="L167">
+        <v>245</v>
+      </c>
+      <c r="M167">
+        <v>255</v>
+      </c>
+      <c r="N167">
+        <v>270</v>
+      </c>
+      <c r="O167">
+        <v>280</v>
+      </c>
+      <c r="P167">
+        <v>290</v>
+      </c>
+      <c r="Q167">
+        <v>292.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F168">
+        <v>155</v>
+      </c>
+      <c r="G168">
+        <v>157.5</v>
+      </c>
+      <c r="H168">
+        <v>162.5</v>
+      </c>
+      <c r="I168">
+        <v>175</v>
+      </c>
+      <c r="J168">
+        <v>202.5</v>
+      </c>
+      <c r="K168">
+        <v>222.5</v>
+      </c>
+      <c r="L168">
+        <v>247.5</v>
+      </c>
+      <c r="M168">
+        <v>245</v>
+      </c>
+      <c r="N168">
+        <v>270</v>
+      </c>
+      <c r="O168">
+        <v>280</v>
+      </c>
+      <c r="P168">
+        <v>287.5</v>
+      </c>
+      <c r="Q168">
+        <v>292.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F169">
+        <v>160</v>
+      </c>
+      <c r="G169">
+        <v>165</v>
+      </c>
+      <c r="H169">
+        <v>170</v>
+      </c>
+      <c r="I169">
+        <v>182.5</v>
+      </c>
+      <c r="J169">
+        <v>212.5</v>
+      </c>
+      <c r="K169">
+        <v>235</v>
+      </c>
+      <c r="L169">
+        <v>257.5</v>
+      </c>
+      <c r="M169">
+        <v>255</v>
+      </c>
+      <c r="N169">
+        <v>285</v>
+      </c>
+      <c r="O169">
+        <v>292.5</v>
+      </c>
+      <c r="P169">
+        <v>300</v>
+      </c>
+      <c r="Q169">
+        <v>307.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F170">
+        <v>22.5</v>
+      </c>
+      <c r="G170">
+        <v>25</v>
+      </c>
+      <c r="H170">
+        <v>30</v>
+      </c>
+      <c r="I170">
+        <v>37.5</v>
+      </c>
+      <c r="J170">
+        <v>40</v>
+      </c>
+      <c r="K170">
+        <v>42.5</v>
+      </c>
+      <c r="L170">
+        <v>45</v>
+      </c>
+      <c r="M170">
+        <v>45</v>
+      </c>
+      <c r="N170">
+        <v>50</v>
+      </c>
+      <c r="O170">
+        <v>52.5</v>
+      </c>
+      <c r="P170">
+        <v>55</v>
+      </c>
+      <c r="Q170">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F171">
+        <v>25</v>
+      </c>
+      <c r="G171">
+        <v>30</v>
+      </c>
+      <c r="H171">
+        <v>35</v>
+      </c>
+      <c r="I171">
+        <v>42.5</v>
+      </c>
+      <c r="J171">
+        <v>42.5</v>
+      </c>
+      <c r="K171">
+        <v>45</v>
+      </c>
+      <c r="L171">
+        <v>45</v>
+      </c>
+      <c r="M171">
+        <v>45</v>
+      </c>
+      <c r="N171">
+        <v>55</v>
+      </c>
+      <c r="O171">
+        <v>57.5</v>
+      </c>
+      <c r="P171">
+        <v>57.5</v>
+      </c>
+      <c r="Q171">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F172">
+        <v>25</v>
+      </c>
+      <c r="G172">
+        <v>30</v>
+      </c>
+      <c r="H172">
+        <v>35</v>
+      </c>
+      <c r="I172">
+        <v>42.5</v>
+      </c>
+      <c r="J172">
+        <v>42.5</v>
+      </c>
+      <c r="K172">
+        <v>45</v>
+      </c>
+      <c r="L172">
+        <v>47.5</v>
+      </c>
+      <c r="M172">
+        <v>47.5</v>
+      </c>
+      <c r="N172">
+        <v>57.5</v>
+      </c>
+      <c r="O172">
+        <v>60</v>
+      </c>
+      <c r="P172">
+        <v>60</v>
+      </c>
+      <c r="Q172">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F173">
+        <v>47.5</v>
+      </c>
+      <c r="G173">
+        <v>52.5</v>
+      </c>
+      <c r="H173">
+        <v>57.5</v>
+      </c>
+      <c r="I173">
+        <v>67.5</v>
+      </c>
+      <c r="J173">
+        <v>67.5</v>
+      </c>
+      <c r="K173">
+        <v>77.5</v>
+      </c>
+      <c r="L173">
+        <v>85</v>
+      </c>
+      <c r="M173">
+        <v>90</v>
+      </c>
+      <c r="N173">
+        <v>95</v>
+      </c>
+      <c r="O173">
+        <v>102.5</v>
+      </c>
+      <c r="P173">
+        <v>107.5</v>
+      </c>
+      <c r="Q173">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F174">
+        <v>50</v>
+      </c>
+      <c r="G174">
+        <v>55</v>
+      </c>
+      <c r="H174">
+        <v>60</v>
+      </c>
+      <c r="I174">
+        <v>72.5</v>
+      </c>
+      <c r="J174">
+        <v>75</v>
+      </c>
+      <c r="K174">
+        <v>82.5</v>
+      </c>
+      <c r="L174">
+        <v>90</v>
+      </c>
+      <c r="M174">
+        <v>95</v>
+      </c>
+      <c r="N174">
+        <v>100</v>
+      </c>
+      <c r="O174">
+        <v>110</v>
+      </c>
+      <c r="P174">
+        <v>112.5</v>
+      </c>
+      <c r="Q174">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F175">
+        <v>52.5</v>
+      </c>
+      <c r="G175">
+        <v>57.5</v>
+      </c>
+      <c r="H175">
+        <v>62.5</v>
+      </c>
+      <c r="I175">
+        <v>75</v>
+      </c>
+      <c r="J175">
+        <v>77.5</v>
+      </c>
+      <c r="K175">
+        <v>85</v>
+      </c>
+      <c r="L175">
+        <v>92.5</v>
+      </c>
+      <c r="M175">
+        <v>100</v>
+      </c>
+      <c r="N175">
+        <v>105</v>
+      </c>
+      <c r="O175">
+        <v>112.5</v>
+      </c>
+      <c r="P175">
+        <v>117.5</v>
+      </c>
+      <c r="Q175">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F176">
+        <v>22.5</v>
+      </c>
+      <c r="G176">
+        <v>25</v>
+      </c>
+      <c r="H176">
+        <v>30</v>
+      </c>
+      <c r="I176">
+        <v>37.5</v>
+      </c>
+      <c r="J176">
+        <v>40</v>
+      </c>
+      <c r="K176">
+        <v>42.5</v>
+      </c>
+      <c r="L176">
+        <v>45</v>
+      </c>
+      <c r="M176">
+        <v>47.5</v>
+      </c>
+      <c r="N176">
+        <v>50</v>
+      </c>
+      <c r="O176">
+        <v>52.5</v>
+      </c>
+      <c r="P176">
+        <v>55</v>
+      </c>
+      <c r="Q176">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F177">
+        <v>25</v>
+      </c>
+      <c r="G177">
+        <v>30</v>
+      </c>
+      <c r="H177">
+        <v>35</v>
+      </c>
+      <c r="I177">
+        <v>42.5</v>
+      </c>
+      <c r="J177">
+        <v>42.5</v>
+      </c>
+      <c r="K177">
+        <v>45</v>
+      </c>
+      <c r="L177">
+        <v>45</v>
+      </c>
+      <c r="M177">
+        <v>52.5</v>
+      </c>
+      <c r="N177">
+        <v>55</v>
+      </c>
+      <c r="O177">
+        <v>57.5</v>
+      </c>
+      <c r="P177">
+        <v>57.5</v>
+      </c>
+      <c r="Q177">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F178">
+        <v>25</v>
+      </c>
+      <c r="G178">
+        <v>30</v>
+      </c>
+      <c r="H178">
+        <v>35</v>
+      </c>
+      <c r="I178">
+        <v>42.5</v>
+      </c>
+      <c r="J178">
+        <v>42.5</v>
+      </c>
+      <c r="K178">
+        <v>45</v>
+      </c>
+      <c r="L178">
+        <v>47.5</v>
+      </c>
+      <c r="M178">
+        <v>55</v>
+      </c>
+      <c r="N178">
+        <v>57.5</v>
+      </c>
+      <c r="O178">
+        <v>60</v>
+      </c>
+      <c r="P178">
+        <v>60</v>
+      </c>
+      <c r="Q178">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A179" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F179">
+        <v>50</v>
+      </c>
+      <c r="G179">
+        <v>55</v>
+      </c>
+      <c r="H179">
+        <v>60</v>
+      </c>
+      <c r="I179">
+        <v>67.5</v>
+      </c>
+      <c r="J179">
+        <v>70</v>
+      </c>
+      <c r="K179">
+        <v>77.5</v>
+      </c>
+      <c r="L179">
+        <v>85</v>
+      </c>
+      <c r="M179">
+        <v>95</v>
+      </c>
+      <c r="N179">
+        <v>97.5</v>
+      </c>
+      <c r="O179">
+        <v>105</v>
+      </c>
+      <c r="P179">
+        <v>110</v>
+      </c>
+      <c r="Q179">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F180">
+        <v>52.5</v>
+      </c>
+      <c r="G180">
+        <v>57.5</v>
+      </c>
+      <c r="H180">
+        <v>62.5</v>
+      </c>
+      <c r="I180">
+        <v>75</v>
+      </c>
+      <c r="J180">
+        <v>75</v>
+      </c>
+      <c r="K180">
+        <v>82.5</v>
+      </c>
+      <c r="L180">
+        <v>90</v>
+      </c>
+      <c r="M180">
+        <v>100</v>
+      </c>
+      <c r="N180">
+        <v>105</v>
+      </c>
+      <c r="O180">
+        <v>110</v>
+      </c>
+      <c r="P180">
+        <v>115</v>
+      </c>
+      <c r="Q180">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A181" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181">
+        <v>55</v>
+      </c>
+      <c r="G181">
+        <v>60</v>
+      </c>
+      <c r="H181">
+        <v>65</v>
+      </c>
+      <c r="I181">
+        <v>77.5</v>
+      </c>
+      <c r="J181">
+        <v>77.5</v>
+      </c>
+      <c r="K181">
+        <v>85</v>
+      </c>
+      <c r="L181">
+        <v>95</v>
+      </c>
+      <c r="M181">
+        <v>105</v>
+      </c>
+      <c r="N181">
+        <v>110</v>
+      </c>
+      <c r="O181">
+        <v>112.5</v>
+      </c>
+      <c r="P181">
+        <v>120</v>
+      </c>
+      <c r="Q181">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q1" xr:uid="{E3552810-31BB-4B88-9769-989F9422D843}"/>
+  <autoFilter ref="A1:Q161" xr:uid="{E3552810-31BB-4B88-9769-989F9422D843}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="60-69"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/FP.xlsx
+++ b/FP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgsafety-my.sharepoint.com/personal/adam_riman_mgsafety_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgsafety-my.sharepoint.com/personal/adam_riman_mgsafety_com/Documents/Desktop/New folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{41426294-6545-418F-89AA-BF24C9B252F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2A6F668-C180-4202-9141-FFA0CF9113AC}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{41426294-6545-418F-89AA-BF24C9B252F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61128A9A-E075-4434-94B5-1A958CC6A9B3}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Men" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Men!$A$1:$Q$321</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Women!$A$1:$Q$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Women!$A$1:$Q$181</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -256,6 +256,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13514,7 +13518,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -13549,7 +13553,7 @@
         <v>285</v>
       </c>
       <c r="L6" s="8">
-        <v>330</v>
+        <v>327.5</v>
       </c>
       <c r="M6" s="8">
         <v>342.5</v>
@@ -13673,7 +13677,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -14097,7 +14101,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -14521,7 +14525,7 @@
         <v>392.5</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -14945,7 +14949,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -15210,7 +15214,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>9</v>
       </c>
@@ -15369,7 +15373,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -15793,7 +15797,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -16217,7 +16221,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -16641,7 +16645,7 @@
         <v>377.5</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -16906,7 +16910,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>9</v>
       </c>
@@ -17065,7 +17069,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -17489,7 +17493,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -17913,7 +17917,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>12</v>
       </c>
@@ -18178,7 +18182,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>9</v>
       </c>
@@ -18337,7 +18341,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>12</v>
       </c>
@@ -18761,7 +18765,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>12</v>
       </c>
@@ -19185,7 +19189,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>12</v>
       </c>
@@ -19450,7 +19454,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>9</v>
       </c>
@@ -19609,7 +19613,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>12</v>
       </c>
@@ -20033,7 +20037,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>12</v>
       </c>
@@ -20457,7 +20461,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>12</v>
       </c>
@@ -20722,7 +20726,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -20881,7 +20885,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>12</v>
       </c>
@@ -21305,7 +21309,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>12</v>
       </c>
@@ -21729,7 +21733,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>12</v>
       </c>
@@ -21782,7 +21786,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>26</v>
       </c>
@@ -21835,7 +21839,7 @@
         <v>257.5</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>26</v>
       </c>
@@ -21888,7 +21892,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>26</v>
       </c>
@@ -21941,7 +21945,7 @@
         <v>322.5</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>26</v>
       </c>
@@ -21994,7 +21998,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>26</v>
       </c>
@@ -22047,7 +22051,7 @@
         <v>257.5</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>26</v>
       </c>
@@ -22100,7 +22104,7 @@
         <v>292.5</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>26</v>
       </c>
@@ -22153,7 +22157,7 @@
         <v>292.5</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>26</v>
       </c>
@@ -22206,7 +22210,7 @@
         <v>307.5</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>26</v>
       </c>
@@ -22259,7 +22263,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>26</v>
       </c>
@@ -22312,7 +22316,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>26</v>
       </c>
@@ -22365,7 +22369,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>26</v>
       </c>
@@ -22418,7 +22422,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>26</v>
       </c>
@@ -22471,7 +22475,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>26</v>
       </c>
@@ -22524,7 +22528,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>26</v>
       </c>
@@ -22577,7 +22581,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>26</v>
       </c>
@@ -22630,7 +22634,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>26</v>
       </c>
@@ -22683,7 +22687,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>26</v>
       </c>
@@ -22736,7 +22740,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>26</v>
       </c>
@@ -22789,7 +22793,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>26</v>
       </c>
@@ -22843,10 +22847,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q161" xr:uid="{E3552810-31BB-4B88-9769-989F9422D843}">
+  <autoFilter ref="A1:Q181" xr:uid="{E3552810-31BB-4B88-9769-989F9422D843}">
     <filterColumn colId="0">
       <filters>
-        <filter val="60-69"/>
+        <filter val="24-39"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Raw"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/FP.xlsx
+++ b/FP.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgsafety-my.sharepoint.com/personal/adam_riman_mgsafety_com/Documents/Desktop/New folder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{41426294-6545-418F-89AA-BF24C9B252F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61128A9A-E075-4434-94B5-1A958CC6A9B3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4D296E-D403-49BC-810E-C51B1F6D2701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Men" sheetId="2" r:id="rId1"/>
     <sheet name="Women" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Men!$A$1:$Q$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Men!$A$1:$Q$341</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Women!$A$1:$Q$181</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -256,10 +256,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -581,17 +577,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Q341"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -644,7 +640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -697,7 +693,7 @@
         <v>502.5</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -750,7 +746,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -803,7 +799,7 @@
         <v>557.5</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -856,7 +852,7 @@
         <v>652.5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -909,7 +905,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -962,7 +958,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1015,7 +1011,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1068,7 +1064,7 @@
         <v>547.5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1121,7 +1117,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -1174,7 +1170,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -1227,7 +1223,7 @@
         <v>637.5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -1280,7 +1276,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1333,7 +1329,7 @@
         <v>877.5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -1386,7 +1382,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -1439,7 +1435,7 @@
         <v>692.5</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -1492,7 +1488,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -1545,7 +1541,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -1598,7 +1594,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -1651,7 +1647,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
@@ -1704,7 +1700,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -1757,7 +1753,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -1810,7 +1806,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
@@ -1863,7 +1859,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -1916,7 +1912,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
@@ -1969,7 +1965,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
@@ -2022,7 +2018,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
@@ -2075,7 +2071,7 @@
         <v>232.5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
@@ -2128,7 +2124,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -2181,7 +2177,7 @@
         <v>317.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -2234,7 +2230,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
@@ -2287,7 +2283,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -2340,7 +2336,7 @@
         <v>227.5</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
@@ -2393,7 +2389,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
@@ -2446,7 +2442,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>7</v>
       </c>
@@ -2499,7 +2495,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
@@ -2552,7 +2548,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>9</v>
       </c>
@@ -2605,7 +2601,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -2658,7 +2654,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -2711,7 +2707,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -2764,7 +2760,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>5</v>
       </c>
@@ -2817,7 +2813,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
@@ -2870,7 +2866,7 @@
         <v>232.5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -2923,7 +2919,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>8</v>
       </c>
@@ -2976,7 +2972,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
@@ -3029,7 +3025,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -3082,7 +3078,7 @@
         <v>312.5</v>
       </c>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
@@ -3135,7 +3131,7 @@
         <v>282.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -3188,7 +3184,7 @@
         <v>252.5</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>5</v>
       </c>
@@ -3241,7 +3237,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
@@ -3294,7 +3290,7 @@
         <v>472.5</v>
       </c>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
@@ -3347,7 +3343,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>8</v>
       </c>
@@ -3400,7 +3396,7 @@
         <v>582.5</v>
       </c>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>9</v>
       </c>
@@ -3453,7 +3449,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -3506,7 +3502,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
@@ -3559,7 +3555,7 @@
         <v>542.5</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -3612,7 +3608,7 @@
         <v>487.5</v>
       </c>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>5</v>
       </c>
@@ -3665,7 +3661,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
@@ -3718,7 +3714,7 @@
         <v>522.5</v>
       </c>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>7</v>
       </c>
@@ -3771,7 +3767,7 @@
         <v>577.5</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>8</v>
       </c>
@@ -3824,7 +3820,7 @@
         <v>677.5</v>
       </c>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>9</v>
       </c>
@@ -3877,7 +3873,7 @@
         <v>797.5</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>10</v>
       </c>
@@ -3930,7 +3926,7 @@
         <v>697.5</v>
       </c>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
@@ -3983,7 +3979,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -4036,7 +4032,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>5</v>
       </c>
@@ -4089,7 +4085,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
@@ -4142,7 +4138,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>7</v>
       </c>
@@ -4195,7 +4191,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>8</v>
       </c>
@@ -4248,7 +4244,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>9</v>
       </c>
@@ -4301,7 +4297,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>10</v>
       </c>
@@ -4354,7 +4350,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -4407,7 +4403,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -4460,7 +4456,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>5</v>
       </c>
@@ -4513,7 +4509,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
@@ -4566,7 +4562,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>7</v>
       </c>
@@ -4619,7 +4615,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>8</v>
       </c>
@@ -4672,7 +4668,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>9</v>
       </c>
@@ -4725,7 +4721,7 @@
         <v>287.5</v>
       </c>
     </row>
-    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>10</v>
       </c>
@@ -4778,7 +4774,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -4831,7 +4827,7 @@
         <v>227.5</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -4884,7 +4880,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>5</v>
       </c>
@@ -4937,7 +4933,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>6</v>
       </c>
@@ -4990,7 +4986,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>7</v>
       </c>
@@ -5043,7 +5039,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>8</v>
       </c>
@@ -5096,7 +5092,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
@@ -5149,7 +5145,7 @@
         <v>182.5</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>10</v>
       </c>
@@ -5202,7 +5198,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -5255,7 +5251,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>12</v>
       </c>
@@ -5308,7 +5304,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>5</v>
       </c>
@@ -5361,7 +5357,7 @@
         <v>202.5</v>
       </c>
     </row>
-    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>6</v>
       </c>
@@ -5414,7 +5410,7 @@
         <v>222.5</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>7</v>
       </c>
@@ -5467,7 +5463,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>8</v>
       </c>
@@ -5520,7 +5516,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>9</v>
       </c>
@@ -5573,7 +5569,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>10</v>
       </c>
@@ -5626,7 +5622,7 @@
         <v>297.5</v>
       </c>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>11</v>
       </c>
@@ -5679,7 +5675,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>12</v>
       </c>
@@ -5732,7 +5728,7 @@
         <v>242.5</v>
       </c>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>5</v>
       </c>
@@ -5785,7 +5781,7 @@
         <v>492.5</v>
       </c>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>6</v>
       </c>
@@ -5838,7 +5834,7 @@
         <v>517.5</v>
       </c>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>7</v>
       </c>
@@ -5891,7 +5887,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>8</v>
       </c>
@@ -5944,7 +5940,7 @@
         <v>637.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>9</v>
       </c>
@@ -5997,7 +5993,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
@@ -6050,7 +6046,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
@@ -6103,7 +6099,7 @@
         <v>592.5</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>12</v>
       </c>
@@ -6156,7 +6152,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>5</v>
       </c>
@@ -6209,7 +6205,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>6</v>
       </c>
@@ -6262,7 +6258,7 @@
         <v>567.5</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>7</v>
       </c>
@@ -6315,7 +6311,7 @@
         <v>627.5</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>8</v>
       </c>
@@ -6368,7 +6364,7 @@
         <v>732.5</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>9</v>
       </c>
@@ -6421,7 +6417,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>10</v>
       </c>
@@ -6474,7 +6470,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -6527,7 +6523,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>12</v>
       </c>
@@ -6580,7 +6576,7 @@
         <v>617.5</v>
       </c>
     </row>
-    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>5</v>
       </c>
@@ -6633,7 +6629,7 @@
         <v>102.5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>6</v>
       </c>
@@ -6686,7 +6682,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>7</v>
       </c>
@@ -6739,7 +6735,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>8</v>
       </c>
@@ -6792,7 +6788,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>9</v>
       </c>
@@ -6845,7 +6841,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>10</v>
       </c>
@@ -6898,7 +6894,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>11</v>
       </c>
@@ -6951,7 +6947,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>12</v>
       </c>
@@ -7004,7 +7000,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>5</v>
       </c>
@@ -7021,43 +7017,43 @@
         <v>16</v>
       </c>
       <c r="F122" s="3">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="G122" s="3">
-        <v>52.5</v>
+        <v>127.5</v>
       </c>
       <c r="H122" s="3">
-        <v>62.5</v>
+        <v>137.5</v>
       </c>
       <c r="I122" s="3">
-        <v>72.5</v>
+        <v>147.5</v>
       </c>
       <c r="J122" s="3">
-        <v>77.5</v>
+        <v>152.5</v>
       </c>
       <c r="K122" s="3">
-        <v>87.5</v>
+        <v>162.5</v>
       </c>
       <c r="L122" s="3">
-        <v>92.5</v>
+        <v>167.5</v>
       </c>
       <c r="M122" s="3">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="N122" s="3">
-        <v>97.5</v>
+        <v>172.5</v>
       </c>
       <c r="O122" s="3">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="P122" s="3">
-        <v>107.5</v>
+        <v>182.5</v>
       </c>
       <c r="Q122" s="3">
-        <v>112.5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>187.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>6</v>
       </c>
@@ -7074,43 +7070,43 @@
         <v>16</v>
       </c>
       <c r="F123" s="3">
-        <v>52.5</v>
+        <v>127.5</v>
       </c>
       <c r="G123" s="3">
-        <v>57.5</v>
+        <v>132.5</v>
       </c>
       <c r="H123" s="3">
-        <v>67.5</v>
+        <v>142.5</v>
       </c>
       <c r="I123" s="3">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="J123" s="3">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="K123" s="3">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="L123" s="3">
-        <v>97.5</v>
+        <v>172.5</v>
       </c>
       <c r="M123" s="3">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="N123" s="3">
-        <v>102.5</v>
+        <v>177.5</v>
       </c>
       <c r="O123" s="3">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="P123" s="3">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="Q123" s="3">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>7</v>
       </c>
@@ -7127,43 +7123,43 @@
         <v>16</v>
       </c>
       <c r="F124" s="3">
-        <v>57.5</v>
+        <v>132.5</v>
       </c>
       <c r="G124" s="3">
-        <v>62.5</v>
+        <v>137.5</v>
       </c>
       <c r="H124" s="3">
-        <v>72.5</v>
+        <v>147.5</v>
       </c>
       <c r="I124" s="3">
-        <v>87.5</v>
+        <v>162.5</v>
       </c>
       <c r="J124" s="3">
-        <v>92.5</v>
+        <v>167.5</v>
       </c>
       <c r="K124" s="3">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="L124" s="3">
-        <v>107.5</v>
+        <v>182.5</v>
       </c>
       <c r="M124" s="3">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="N124" s="3">
-        <v>112.5</v>
+        <v>187.5</v>
       </c>
       <c r="O124" s="3">
-        <v>122.5</v>
+        <v>197.5</v>
       </c>
       <c r="P124" s="3">
-        <v>132.5</v>
+        <v>207.5</v>
       </c>
       <c r="Q124" s="3">
-        <v>137.5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>212.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>8</v>
       </c>
@@ -7180,43 +7176,43 @@
         <v>16</v>
       </c>
       <c r="F125" s="3">
-        <v>62.5</v>
+        <v>137.5</v>
       </c>
       <c r="G125" s="3">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="H125" s="3">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="I125" s="3">
-        <v>97.5</v>
+        <v>172.5</v>
       </c>
       <c r="J125" s="3">
-        <v>102.5</v>
+        <v>177.5</v>
       </c>
       <c r="K125" s="3">
-        <v>117.5</v>
+        <v>192.5</v>
       </c>
       <c r="L125" s="3">
-        <v>122.5</v>
+        <v>197.5</v>
       </c>
       <c r="M125" s="3">
-        <v>127.5</v>
+        <v>202.5</v>
       </c>
       <c r="N125" s="3">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="O125" s="3">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="P125" s="3">
-        <v>152.5</v>
+        <v>227.5</v>
       </c>
       <c r="Q125" s="3">
-        <v>157.5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>232.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
@@ -7233,43 +7229,43 @@
         <v>16</v>
       </c>
       <c r="F126" s="3">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G126" s="3">
-        <v>87.5</v>
+        <v>162.5</v>
       </c>
       <c r="H126" s="3">
-        <v>87.5</v>
+        <v>162.5</v>
       </c>
       <c r="I126" s="3">
-        <v>117.5</v>
+        <v>192.5</v>
       </c>
       <c r="J126" s="3">
-        <v>122.5</v>
+        <v>197.5</v>
       </c>
       <c r="K126" s="3">
-        <v>137.5</v>
+        <v>212.5</v>
       </c>
       <c r="L126" s="3">
-        <v>142.5</v>
+        <v>217.5</v>
       </c>
       <c r="M126" s="3">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="N126" s="3">
-        <v>157.5</v>
+        <v>232.5</v>
       </c>
       <c r="O126" s="3">
-        <v>162.5</v>
+        <v>237.5</v>
       </c>
       <c r="P126" s="3">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="Q126" s="3">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -7286,43 +7282,43 @@
         <v>16</v>
       </c>
       <c r="F127" s="3">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="G127" s="3">
-        <v>77.5</v>
+        <v>152.5</v>
       </c>
       <c r="H127" s="3">
-        <v>77.5</v>
+        <v>152.5</v>
       </c>
       <c r="I127" s="3">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="J127" s="3">
-        <v>107.5</v>
+        <v>182.5</v>
       </c>
       <c r="K127" s="3">
-        <v>122.5</v>
+        <v>197.5</v>
       </c>
       <c r="L127" s="3">
-        <v>122.5</v>
+        <v>197.5</v>
       </c>
       <c r="M127" s="3">
-        <v>130</v>
+        <v>205</v>
       </c>
       <c r="N127" s="3">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="O127" s="3">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="P127" s="3">
-        <v>157.5</v>
+        <v>232.5</v>
       </c>
       <c r="Q127" s="3">
-        <v>162.5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>237.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>11</v>
       </c>
@@ -7339,43 +7335,43 @@
         <v>16</v>
       </c>
       <c r="F128" s="3">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="G128" s="3">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="H128" s="3">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="I128" s="3">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="J128" s="3">
-        <v>97.5</v>
+        <v>172.5</v>
       </c>
       <c r="K128" s="3">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="L128" s="3">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="M128" s="3">
-        <v>117.5</v>
+        <v>192.5</v>
       </c>
       <c r="N128" s="3">
-        <v>127.5</v>
+        <v>202.5</v>
       </c>
       <c r="O128" s="3">
-        <v>130</v>
+        <v>205</v>
       </c>
       <c r="P128" s="3">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="Q128" s="3">
-        <v>147.5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+        <v>222.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>12</v>
       </c>
@@ -7392,43 +7388,43 @@
         <v>16</v>
       </c>
       <c r="F129" s="3">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="G129" s="3">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="H129" s="3">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="I129" s="3">
-        <v>87.5</v>
+        <v>162.5</v>
       </c>
       <c r="J129" s="3">
-        <v>92.5</v>
+        <v>167.5</v>
       </c>
       <c r="K129" s="3">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="L129" s="3">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="M129" s="3">
-        <v>107.5</v>
+        <v>182.5</v>
       </c>
       <c r="N129" s="3">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="O129" s="3">
-        <v>117.5</v>
+        <v>192.5</v>
       </c>
       <c r="P129" s="3">
-        <v>130</v>
+        <v>205</v>
       </c>
       <c r="Q129" s="3">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>5</v>
       </c>
@@ -7481,7 +7477,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>6</v>
       </c>
@@ -7534,7 +7530,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>7</v>
       </c>
@@ -7587,7 +7583,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>8</v>
       </c>
@@ -7640,7 +7636,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
@@ -7693,7 +7689,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>10</v>
       </c>
@@ -7746,7 +7742,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>11</v>
       </c>
@@ -7799,7 +7795,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>12</v>
       </c>
@@ -7852,7 +7848,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>5</v>
       </c>
@@ -7905,7 +7901,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>6</v>
       </c>
@@ -7958,7 +7954,7 @@
         <v>222.5</v>
       </c>
     </row>
-    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>7</v>
       </c>
@@ -8011,7 +8007,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>8</v>
       </c>
@@ -8064,7 +8060,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -8117,7 +8113,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
@@ -8170,7 +8166,7 @@
         <v>297.5</v>
       </c>
     </row>
-    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>11</v>
       </c>
@@ -8223,7 +8219,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>12</v>
       </c>
@@ -8276,7 +8272,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>5</v>
       </c>
@@ -8329,7 +8325,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>6</v>
       </c>
@@ -8382,7 +8378,7 @@
         <v>502.5</v>
       </c>
     </row>
-    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>7</v>
       </c>
@@ -8435,7 +8431,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>8</v>
       </c>
@@ -8488,7 +8484,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>9</v>
       </c>
@@ -8541,7 +8537,7 @@
         <v>727.5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>10</v>
       </c>
@@ -8594,7 +8590,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -8647,7 +8643,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>12</v>
       </c>
@@ -8700,7 +8696,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>5</v>
       </c>
@@ -8753,7 +8749,7 @@
         <v>492.5</v>
       </c>
     </row>
-    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>6</v>
       </c>
@@ -8806,7 +8802,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>7</v>
       </c>
@@ -8859,7 +8855,7 @@
         <v>607.5</v>
       </c>
     </row>
-    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>8</v>
       </c>
@@ -8912,7 +8908,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>9</v>
       </c>
@@ -8965,7 +8961,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -9018,7 +9014,7 @@
         <v>732.5</v>
       </c>
     </row>
-    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>11</v>
       </c>
@@ -9071,7 +9067,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>12</v>
       </c>
@@ -9124,7 +9120,7 @@
         <v>597.5</v>
       </c>
     </row>
-    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -9143,7 +9139,7 @@
       <c r="P162" s="3"/>
       <c r="Q162" s="3"/>
     </row>
-    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -9162,7 +9158,7 @@
       <c r="P163" s="3"/>
       <c r="Q163" s="3"/>
     </row>
-    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -9181,7 +9177,7 @@
       <c r="P164" s="3"/>
       <c r="Q164" s="3"/>
     </row>
-    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -9200,7 +9196,7 @@
       <c r="P165" s="3"/>
       <c r="Q165" s="3"/>
     </row>
-    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -9219,7 +9215,7 @@
       <c r="P166" s="3"/>
       <c r="Q166" s="3"/>
     </row>
-    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -9238,7 +9234,7 @@
       <c r="P167" s="3"/>
       <c r="Q167" s="3"/>
     </row>
-    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -9257,7 +9253,7 @@
       <c r="P168" s="3"/>
       <c r="Q168" s="3"/>
     </row>
-    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -9276,7 +9272,7 @@
       <c r="P169" s="3"/>
       <c r="Q169" s="3"/>
     </row>
-    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -9295,7 +9291,7 @@
       <c r="P170" s="3"/>
       <c r="Q170" s="3"/>
     </row>
-    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -9314,7 +9310,7 @@
       <c r="P171" s="3"/>
       <c r="Q171" s="3"/>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -9333,7 +9329,7 @@
       <c r="P172" s="3"/>
       <c r="Q172" s="3"/>
     </row>
-    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -9352,7 +9348,7 @@
       <c r="P173" s="3"/>
       <c r="Q173" s="3"/>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -9371,7 +9367,7 @@
       <c r="P174" s="3"/>
       <c r="Q174" s="3"/>
     </row>
-    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -9390,7 +9386,7 @@
       <c r="P175" s="3"/>
       <c r="Q175" s="3"/>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -9409,7 +9405,7 @@
       <c r="P176" s="3"/>
       <c r="Q176" s="3"/>
     </row>
-    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -9428,7 +9424,7 @@
       <c r="P177" s="3"/>
       <c r="Q177" s="3"/>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -9447,7 +9443,7 @@
       <c r="P178" s="3"/>
       <c r="Q178" s="3"/>
     </row>
-    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -9466,7 +9462,7 @@
       <c r="P179" s="3"/>
       <c r="Q179" s="3"/>
     </row>
-    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -9485,7 +9481,7 @@
       <c r="P180" s="3"/>
       <c r="Q180" s="3"/>
     </row>
-    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -9504,7 +9500,7 @@
       <c r="P181" s="3"/>
       <c r="Q181" s="3"/>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -9523,7 +9519,7 @@
       <c r="P182" s="3"/>
       <c r="Q182" s="3"/>
     </row>
-    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -9542,7 +9538,7 @@
       <c r="P183" s="3"/>
       <c r="Q183" s="3"/>
     </row>
-    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -9561,7 +9557,7 @@
       <c r="P184" s="3"/>
       <c r="Q184" s="3"/>
     </row>
-    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -9580,7 +9576,7 @@
       <c r="P185" s="3"/>
       <c r="Q185" s="3"/>
     </row>
-    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -9599,7 +9595,7 @@
       <c r="P186" s="3"/>
       <c r="Q186" s="3"/>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -9618,7 +9614,7 @@
       <c r="P187" s="3"/>
       <c r="Q187" s="3"/>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -9637,7 +9633,7 @@
       <c r="P188" s="3"/>
       <c r="Q188" s="3"/>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -9656,7 +9652,7 @@
       <c r="P189" s="3"/>
       <c r="Q189" s="3"/>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -9675,7 +9671,7 @@
       <c r="P190" s="3"/>
       <c r="Q190" s="3"/>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -9694,7 +9690,7 @@
       <c r="P191" s="3"/>
       <c r="Q191" s="3"/>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -9713,7 +9709,7 @@
       <c r="P192" s="3"/>
       <c r="Q192" s="3"/>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -9732,7 +9728,7 @@
       <c r="P193" s="3"/>
       <c r="Q193" s="3"/>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -9751,7 +9747,7 @@
       <c r="P194" s="5"/>
       <c r="Q194" s="5"/>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -9770,7 +9766,7 @@
       <c r="P195" s="5"/>
       <c r="Q195" s="5"/>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -9789,7 +9785,7 @@
       <c r="P196" s="5"/>
       <c r="Q196" s="5"/>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -9808,7 +9804,7 @@
       <c r="P197" s="5"/>
       <c r="Q197" s="5"/>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -9827,7 +9823,7 @@
       <c r="P198" s="5"/>
       <c r="Q198" s="5"/>
     </row>
-    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -9846,7 +9842,7 @@
       <c r="P199" s="5"/>
       <c r="Q199" s="5"/>
     </row>
-    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -9865,7 +9861,7 @@
       <c r="P200" s="5"/>
       <c r="Q200" s="5"/>
     </row>
-    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -9884,7 +9880,7 @@
       <c r="P201" s="5"/>
       <c r="Q201" s="5"/>
     </row>
-    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -9903,7 +9899,7 @@
       <c r="P202" s="5"/>
       <c r="Q202" s="5"/>
     </row>
-    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -9922,7 +9918,7 @@
       <c r="P203" s="5"/>
       <c r="Q203" s="5"/>
     </row>
-    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -9941,7 +9937,7 @@
       <c r="P204" s="5"/>
       <c r="Q204" s="5"/>
     </row>
-    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -9960,7 +9956,7 @@
       <c r="P205" s="5"/>
       <c r="Q205" s="5"/>
     </row>
-    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -9979,7 +9975,7 @@
       <c r="P206" s="5"/>
       <c r="Q206" s="5"/>
     </row>
-    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -9998,7 +9994,7 @@
       <c r="P207" s="5"/>
       <c r="Q207" s="5"/>
     </row>
-    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -10017,7 +10013,7 @@
       <c r="P208" s="5"/>
       <c r="Q208" s="5"/>
     </row>
-    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -10036,7 +10032,7 @@
       <c r="P209" s="5"/>
       <c r="Q209" s="5"/>
     </row>
-    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -10055,7 +10051,7 @@
       <c r="P210" s="5"/>
       <c r="Q210" s="5"/>
     </row>
-    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -10074,7 +10070,7 @@
       <c r="P211" s="5"/>
       <c r="Q211" s="5"/>
     </row>
-    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -10093,7 +10089,7 @@
       <c r="P212" s="5"/>
       <c r="Q212" s="5"/>
     </row>
-    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -10112,7 +10108,7 @@
       <c r="P213" s="5"/>
       <c r="Q213" s="5"/>
     </row>
-    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -10131,7 +10127,7 @@
       <c r="P214" s="5"/>
       <c r="Q214" s="5"/>
     </row>
-    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -10150,7 +10146,7 @@
       <c r="P215" s="5"/>
       <c r="Q215" s="5"/>
     </row>
-    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -10169,7 +10165,7 @@
       <c r="P216" s="5"/>
       <c r="Q216" s="5"/>
     </row>
-    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -10188,7 +10184,7 @@
       <c r="P217" s="5"/>
       <c r="Q217" s="5"/>
     </row>
-    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -10207,7 +10203,7 @@
       <c r="P218" s="5"/>
       <c r="Q218" s="5"/>
     </row>
-    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -10226,7 +10222,7 @@
       <c r="P219" s="5"/>
       <c r="Q219" s="5"/>
     </row>
-    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -10245,7 +10241,7 @@
       <c r="P220" s="5"/>
       <c r="Q220" s="5"/>
     </row>
-    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -10264,7 +10260,7 @@
       <c r="P221" s="5"/>
       <c r="Q221" s="5"/>
     </row>
-    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -10283,7 +10279,7 @@
       <c r="P222" s="5"/>
       <c r="Q222" s="5"/>
     </row>
-    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -10302,7 +10298,7 @@
       <c r="P223" s="5"/>
       <c r="Q223" s="5"/>
     </row>
-    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -10321,7 +10317,7 @@
       <c r="P224" s="5"/>
       <c r="Q224" s="5"/>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -10340,7 +10336,7 @@
       <c r="P225" s="5"/>
       <c r="Q225" s="5"/>
     </row>
-    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -10359,7 +10355,7 @@
       <c r="P226" s="3"/>
       <c r="Q226" s="3"/>
     </row>
-    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -10378,7 +10374,7 @@
       <c r="P227" s="3"/>
       <c r="Q227" s="3"/>
     </row>
-    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -10397,7 +10393,7 @@
       <c r="P228" s="3"/>
       <c r="Q228" s="3"/>
     </row>
-    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -10416,7 +10412,7 @@
       <c r="P229" s="3"/>
       <c r="Q229" s="3"/>
     </row>
-    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -10435,7 +10431,7 @@
       <c r="P230" s="3"/>
       <c r="Q230" s="3"/>
     </row>
-    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -10454,7 +10450,7 @@
       <c r="P231" s="3"/>
       <c r="Q231" s="3"/>
     </row>
-    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -10473,7 +10469,7 @@
       <c r="P232" s="3"/>
       <c r="Q232" s="3"/>
     </row>
-    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -10492,7 +10488,7 @@
       <c r="P233" s="3"/>
       <c r="Q233" s="3"/>
     </row>
-    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -10511,7 +10507,7 @@
       <c r="P234" s="5"/>
       <c r="Q234" s="5"/>
     </row>
-    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -10530,7 +10526,7 @@
       <c r="P235" s="5"/>
       <c r="Q235" s="5"/>
     </row>
-    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -10549,7 +10545,7 @@
       <c r="P236" s="5"/>
       <c r="Q236" s="5"/>
     </row>
-    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -10568,7 +10564,7 @@
       <c r="P237" s="5"/>
       <c r="Q237" s="5"/>
     </row>
-    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -10587,7 +10583,7 @@
       <c r="P238" s="5"/>
       <c r="Q238" s="5"/>
     </row>
-    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -10606,7 +10602,7 @@
       <c r="P239" s="5"/>
       <c r="Q239" s="5"/>
     </row>
-    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -10625,7 +10621,7 @@
       <c r="P240" s="5"/>
       <c r="Q240" s="5"/>
     </row>
-    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -10644,7 +10640,7 @@
       <c r="P241" s="5"/>
       <c r="Q241" s="5"/>
     </row>
-    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -10663,7 +10659,7 @@
       <c r="P242" s="3"/>
       <c r="Q242" s="3"/>
     </row>
-    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -10682,7 +10678,7 @@
       <c r="P243" s="3"/>
       <c r="Q243" s="3"/>
     </row>
-    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -10701,7 +10697,7 @@
       <c r="P244" s="3"/>
       <c r="Q244" s="3"/>
     </row>
-    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -10720,7 +10716,7 @@
       <c r="P245" s="3"/>
       <c r="Q245" s="3"/>
     </row>
-    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -10739,7 +10735,7 @@
       <c r="P246" s="3"/>
       <c r="Q246" s="3"/>
     </row>
-    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -10758,7 +10754,7 @@
       <c r="P247" s="3"/>
       <c r="Q247" s="3"/>
     </row>
-    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -10777,7 +10773,7 @@
       <c r="P248" s="3"/>
       <c r="Q248" s="3"/>
     </row>
-    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -10796,7 +10792,7 @@
       <c r="P249" s="3"/>
       <c r="Q249" s="3"/>
     </row>
-    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -10815,7 +10811,7 @@
       <c r="P250" s="3"/>
       <c r="Q250" s="3"/>
     </row>
-    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -10834,7 +10830,7 @@
       <c r="P251" s="3"/>
       <c r="Q251" s="3"/>
     </row>
-    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -10853,7 +10849,7 @@
       <c r="P252" s="3"/>
       <c r="Q252" s="3"/>
     </row>
-    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -10872,7 +10868,7 @@
       <c r="P253" s="3"/>
       <c r="Q253" s="3"/>
     </row>
-    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -10891,7 +10887,7 @@
       <c r="P254" s="3"/>
       <c r="Q254" s="3"/>
     </row>
-    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -10910,7 +10906,7 @@
       <c r="P255" s="3"/>
       <c r="Q255" s="3"/>
     </row>
-    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -10929,7 +10925,7 @@
       <c r="P256" s="3"/>
       <c r="Q256" s="3"/>
     </row>
-    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -10948,7 +10944,7 @@
       <c r="P257" s="3"/>
       <c r="Q257" s="3"/>
     </row>
-    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -10967,7 +10963,7 @@
       <c r="P258" s="5"/>
       <c r="Q258" s="5"/>
     </row>
-    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -10986,7 +10982,7 @@
       <c r="P259" s="5"/>
       <c r="Q259" s="5"/>
     </row>
-    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -11005,7 +11001,7 @@
       <c r="P260" s="5"/>
       <c r="Q260" s="5"/>
     </row>
-    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -11024,7 +11020,7 @@
       <c r="P261" s="5"/>
       <c r="Q261" s="5"/>
     </row>
-    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -11043,7 +11039,7 @@
       <c r="P262" s="5"/>
       <c r="Q262" s="5"/>
     </row>
-    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -11062,7 +11058,7 @@
       <c r="P263" s="5"/>
       <c r="Q263" s="5"/>
     </row>
-    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -11081,7 +11077,7 @@
       <c r="P264" s="5"/>
       <c r="Q264" s="5"/>
     </row>
-    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -11100,7 +11096,7 @@
       <c r="P265" s="5"/>
       <c r="Q265" s="5"/>
     </row>
-    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -11119,7 +11115,7 @@
       <c r="P266" s="3"/>
       <c r="Q266" s="3"/>
     </row>
-    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -11138,7 +11134,7 @@
       <c r="P267" s="3"/>
       <c r="Q267" s="3"/>
     </row>
-    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -11157,7 +11153,7 @@
       <c r="P268" s="3"/>
       <c r="Q268" s="3"/>
     </row>
-    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -11176,7 +11172,7 @@
       <c r="P269" s="3"/>
       <c r="Q269" s="3"/>
     </row>
-    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -11195,7 +11191,7 @@
       <c r="P270" s="3"/>
       <c r="Q270" s="3"/>
     </row>
-    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -11214,7 +11210,7 @@
       <c r="P271" s="3"/>
       <c r="Q271" s="3"/>
     </row>
-    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -11233,7 +11229,7 @@
       <c r="P272" s="3"/>
       <c r="Q272" s="3"/>
     </row>
-    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -11252,7 +11248,7 @@
       <c r="P273" s="3"/>
       <c r="Q273" s="3"/>
     </row>
-    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -11271,7 +11267,7 @@
       <c r="P274" s="3"/>
       <c r="Q274" s="3"/>
     </row>
-    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -11290,7 +11286,7 @@
       <c r="P275" s="3"/>
       <c r="Q275" s="3"/>
     </row>
-    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -11309,7 +11305,7 @@
       <c r="P276" s="3"/>
       <c r="Q276" s="3"/>
     </row>
-    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -11328,7 +11324,7 @@
       <c r="P277" s="3"/>
       <c r="Q277" s="3"/>
     </row>
-    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -11347,7 +11343,7 @@
       <c r="P278" s="3"/>
       <c r="Q278" s="3"/>
     </row>
-    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -11366,7 +11362,7 @@
       <c r="P279" s="3"/>
       <c r="Q279" s="3"/>
     </row>
-    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -11385,7 +11381,7 @@
       <c r="P280" s="3"/>
       <c r="Q280" s="3"/>
     </row>
-    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -11404,7 +11400,7 @@
       <c r="P281" s="3"/>
       <c r="Q281" s="3"/>
     </row>
-    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -11423,7 +11419,7 @@
       <c r="P282" s="3"/>
       <c r="Q282" s="3"/>
     </row>
-    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -11442,7 +11438,7 @@
       <c r="P283" s="3"/>
       <c r="Q283" s="3"/>
     </row>
-    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -11461,7 +11457,7 @@
       <c r="P284" s="3"/>
       <c r="Q284" s="3"/>
     </row>
-    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -11480,7 +11476,7 @@
       <c r="P285" s="3"/>
       <c r="Q285" s="3"/>
     </row>
-    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -11499,7 +11495,7 @@
       <c r="P286" s="3"/>
       <c r="Q286" s="3"/>
     </row>
-    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -11518,7 +11514,7 @@
       <c r="P287" s="3"/>
       <c r="Q287" s="3"/>
     </row>
-    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -11537,7 +11533,7 @@
       <c r="P288" s="3"/>
       <c r="Q288" s="3"/>
     </row>
-    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -11556,7 +11552,7 @@
       <c r="P289" s="3"/>
       <c r="Q289" s="3"/>
     </row>
-    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -11575,7 +11571,7 @@
       <c r="P290" s="3"/>
       <c r="Q290" s="3"/>
     </row>
-    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -11594,7 +11590,7 @@
       <c r="P291" s="3"/>
       <c r="Q291" s="3"/>
     </row>
-    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -11613,7 +11609,7 @@
       <c r="P292" s="3"/>
       <c r="Q292" s="3"/>
     </row>
-    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -11632,7 +11628,7 @@
       <c r="P293" s="3"/>
       <c r="Q293" s="3"/>
     </row>
-    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -11651,7 +11647,7 @@
       <c r="P294" s="3"/>
       <c r="Q294" s="3"/>
     </row>
-    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -11670,7 +11666,7 @@
       <c r="P295" s="3"/>
       <c r="Q295" s="3"/>
     </row>
-    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -11689,7 +11685,7 @@
       <c r="P296" s="3"/>
       <c r="Q296" s="3"/>
     </row>
-    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -11708,7 +11704,7 @@
       <c r="P297" s="3"/>
       <c r="Q297" s="3"/>
     </row>
-    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -11727,7 +11723,7 @@
       <c r="P298" s="3"/>
       <c r="Q298" s="3"/>
     </row>
-    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -11746,7 +11742,7 @@
       <c r="P299" s="3"/>
       <c r="Q299" s="3"/>
     </row>
-    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -11765,7 +11761,7 @@
       <c r="P300" s="3"/>
       <c r="Q300" s="3"/>
     </row>
-    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -11784,7 +11780,7 @@
       <c r="P301" s="3"/>
       <c r="Q301" s="3"/>
     </row>
-    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -11803,7 +11799,7 @@
       <c r="P302" s="3"/>
       <c r="Q302" s="3"/>
     </row>
-    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -11822,7 +11818,7 @@
       <c r="P303" s="3"/>
       <c r="Q303" s="3"/>
     </row>
-    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -11841,7 +11837,7 @@
       <c r="P304" s="3"/>
       <c r="Q304" s="3"/>
     </row>
-    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -11860,7 +11856,7 @@
       <c r="P305" s="3"/>
       <c r="Q305" s="3"/>
     </row>
-    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -11879,7 +11875,7 @@
       <c r="P306" s="5"/>
       <c r="Q306" s="5"/>
     </row>
-    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -11898,7 +11894,7 @@
       <c r="P307" s="5"/>
       <c r="Q307" s="5"/>
     </row>
-    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -11917,7 +11913,7 @@
       <c r="P308" s="5"/>
       <c r="Q308" s="5"/>
     </row>
-    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -11936,7 +11932,7 @@
       <c r="P309" s="5"/>
       <c r="Q309" s="5"/>
     </row>
-    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -11955,7 +11951,7 @@
       <c r="P310" s="5"/>
       <c r="Q310" s="5"/>
     </row>
-    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -11974,7 +11970,7 @@
       <c r="P311" s="5"/>
       <c r="Q311" s="5"/>
     </row>
-    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -11993,7 +11989,7 @@
       <c r="P312" s="5"/>
       <c r="Q312" s="5"/>
     </row>
-    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -12012,7 +12008,7 @@
       <c r="P313" s="5"/>
       <c r="Q313" s="5"/>
     </row>
-    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -12031,7 +12027,7 @@
       <c r="P314" s="3"/>
       <c r="Q314" s="3"/>
     </row>
-    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -12050,7 +12046,7 @@
       <c r="P315" s="3"/>
       <c r="Q315" s="3"/>
     </row>
-    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -12069,7 +12065,7 @@
       <c r="P316" s="3"/>
       <c r="Q316" s="3"/>
     </row>
-    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -12088,7 +12084,7 @@
       <c r="P317" s="3"/>
       <c r="Q317" s="3"/>
     </row>
-    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -12107,7 +12103,7 @@
       <c r="P318" s="3"/>
       <c r="Q318" s="3"/>
     </row>
-    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -12126,7 +12122,7 @@
       <c r="P319" s="3"/>
       <c r="Q319" s="3"/>
     </row>
-    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -12145,7 +12141,7 @@
       <c r="P320" s="3"/>
       <c r="Q320" s="3"/>
     </row>
-    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -12164,7 +12160,7 @@
       <c r="P321" s="3"/>
       <c r="Q321" s="3"/>
     </row>
-    <row r="322" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>26</v>
       </c>
@@ -12217,7 +12213,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="323" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>26</v>
       </c>
@@ -12270,7 +12266,7 @@
         <v>562.5</v>
       </c>
     </row>
-    <row r="324" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>26</v>
       </c>
@@ -12323,7 +12319,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="325" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>26</v>
       </c>
@@ -12376,7 +12372,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="326" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>26</v>
       </c>
@@ -12429,7 +12425,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="327" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>26</v>
       </c>
@@ -12482,7 +12478,7 @@
         <v>227.5</v>
       </c>
     </row>
-    <row r="328" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>26</v>
       </c>
@@ -12535,7 +12531,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="329" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>26</v>
       </c>
@@ -12588,7 +12584,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="330" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>26</v>
       </c>
@@ -12641,7 +12637,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="331" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>26</v>
       </c>
@@ -12694,7 +12690,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="332" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>26</v>
       </c>
@@ -12747,7 +12743,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="333" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>26</v>
       </c>
@@ -12800,7 +12796,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="334" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>26</v>
       </c>
@@ -12853,7 +12849,7 @@
         <v>482.5</v>
       </c>
     </row>
-    <row r="335" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>26</v>
       </c>
@@ -12906,7 +12902,7 @@
         <v>557.5</v>
       </c>
     </row>
-    <row r="336" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>26</v>
       </c>
@@ -12959,7 +12955,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>26</v>
       </c>
@@ -12975,44 +12971,44 @@
       <c r="E337" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F337" s="1">
-        <v>50</v>
-      </c>
-      <c r="G337" s="1">
-        <v>60</v>
-      </c>
-      <c r="H337" s="1">
-        <v>60</v>
-      </c>
-      <c r="I337" s="1">
-        <v>80</v>
-      </c>
-      <c r="J337" s="1">
-        <v>85</v>
-      </c>
-      <c r="K337" s="1">
-        <v>90</v>
-      </c>
-      <c r="L337" s="1">
-        <v>90</v>
-      </c>
-      <c r="M337" s="1">
-        <v>97.5</v>
-      </c>
-      <c r="N337" s="1">
-        <v>105</v>
-      </c>
-      <c r="O337" s="1">
-        <v>107.5</v>
-      </c>
-      <c r="P337" s="1">
-        <v>117.5</v>
-      </c>
-      <c r="Q337" s="1">
-        <v>122.5</v>
-      </c>
-    </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F337" s="3">
+        <v>125</v>
+      </c>
+      <c r="G337" s="3">
+        <v>135</v>
+      </c>
+      <c r="H337" s="3">
+        <v>135</v>
+      </c>
+      <c r="I337" s="3">
+        <v>155</v>
+      </c>
+      <c r="J337" s="3">
+        <v>160</v>
+      </c>
+      <c r="K337" s="3">
+        <v>165</v>
+      </c>
+      <c r="L337" s="3">
+        <v>165</v>
+      </c>
+      <c r="M337" s="3">
+        <v>172.5</v>
+      </c>
+      <c r="N337" s="3">
+        <v>180</v>
+      </c>
+      <c r="O337" s="3">
+        <v>182.5</v>
+      </c>
+      <c r="P337" s="3">
+        <v>192.5</v>
+      </c>
+      <c r="Q337" s="3">
+        <v>197.5</v>
+      </c>
+    </row>
+    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>26</v>
       </c>
@@ -13065,7 +13061,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>26</v>
       </c>
@@ -13118,7 +13114,7 @@
         <v>217.5</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>26</v>
       </c>
@@ -13171,7 +13167,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>26</v>
       </c>
@@ -13225,16 +13221,26 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q321" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="60-69"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:Q341" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="D"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Yes"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Single-ply"/>
+      </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q161">
       <sortCondition ref="E1:E321"/>
@@ -13246,14 +13252,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3552810-31BB-4B88-9769-989F9422D843}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q181"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -13306,7 +13311,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -13359,7 +13364,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -13412,7 +13417,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -13465,7 +13470,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -13518,7 +13523,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -13571,7 +13576,7 @@
         <v>397.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -13624,7 +13629,7 @@
         <v>347.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -13677,7 +13682,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -13730,7 +13735,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -13783,7 +13788,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -13836,7 +13841,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -13889,7 +13894,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -13942,7 +13947,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -13995,7 +14000,7 @@
         <v>427.5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -14048,7 +14053,7 @@
         <v>377.5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -14101,7 +14106,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -14154,7 +14159,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -14207,7 +14212,7 @@
         <v>327.5</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -14260,7 +14265,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -14313,7 +14318,7 @@
         <v>362.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>8</v>
       </c>
@@ -14366,7 +14371,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -14419,7 +14424,7 @@
         <v>492.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -14472,7 +14477,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
@@ -14525,7 +14530,7 @@
         <v>392.5</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -14578,7 +14583,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
@@ -14631,7 +14636,7 @@
         <v>342.5</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
@@ -14684,7 +14689,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
@@ -14737,7 +14742,7 @@
         <v>377.5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
@@ -14790,7 +14795,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -14843,7 +14848,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -14896,7 +14901,7 @@
         <v>452.5</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
@@ -14949,7 +14954,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -15002,7 +15007,7 @@
         <v>372.5</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
@@ -15055,7 +15060,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
@@ -15108,7 +15113,7 @@
         <v>262.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>7</v>
       </c>
@@ -15161,7 +15166,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>8</v>
       </c>
@@ -15214,7 +15219,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>9</v>
       </c>
@@ -15267,7 +15272,7 @@
         <v>422.5</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -15320,7 +15325,7 @@
         <v>347.5</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -15373,7 +15378,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -15426,7 +15431,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>5</v>
       </c>
@@ -15479,7 +15484,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
@@ -15532,7 +15537,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -15585,7 +15590,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>8</v>
       </c>
@@ -15638,7 +15643,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
@@ -15691,7 +15696,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -15744,7 +15749,7 @@
         <v>397.5</v>
       </c>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
@@ -15797,7 +15802,7 @@
         <v>357.5</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -15850,7 +15855,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>5</v>
       </c>
@@ -15903,7 +15908,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
@@ -15956,7 +15961,7 @@
         <v>297.5</v>
       </c>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
@@ -16009,7 +16014,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>8</v>
       </c>
@@ -16062,7 +16067,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>9</v>
       </c>
@@ -16115,7 +16120,7 @@
         <v>452.5</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -16168,7 +16173,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
@@ -16221,7 +16226,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -16274,7 +16279,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>5</v>
       </c>
@@ -16327,7 +16332,7 @@
         <v>282.5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
@@ -16380,7 +16385,7 @@
         <v>312.5</v>
       </c>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>7</v>
       </c>
@@ -16433,7 +16438,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>8</v>
       </c>
@@ -16486,7 +16491,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>9</v>
       </c>
@@ -16539,7 +16544,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>10</v>
       </c>
@@ -16592,7 +16597,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
@@ -16645,7 +16650,7 @@
         <v>377.5</v>
       </c>
     </row>
-    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -16698,7 +16703,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>5</v>
       </c>
@@ -16751,7 +16756,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
@@ -16804,7 +16809,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>7</v>
       </c>
@@ -16857,7 +16862,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>8</v>
       </c>
@@ -16910,7 +16915,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>9</v>
       </c>
@@ -16963,7 +16968,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>10</v>
       </c>
@@ -17016,7 +17021,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -17069,7 +17074,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -17122,7 +17127,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>5</v>
       </c>
@@ -17175,7 +17180,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
@@ -17228,7 +17233,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>7</v>
       </c>
@@ -17281,7 +17286,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>8</v>
       </c>
@@ -17334,7 +17339,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>9</v>
       </c>
@@ -17387,7 +17392,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>10</v>
       </c>
@@ -17440,7 +17445,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -17493,7 +17498,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -17546,7 +17551,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>5</v>
       </c>
@@ -17599,7 +17604,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>6</v>
       </c>
@@ -17652,7 +17657,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>7</v>
       </c>
@@ -17705,7 +17710,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>8</v>
       </c>
@@ -17758,7 +17763,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
@@ -17811,7 +17816,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>10</v>
       </c>
@@ -17864,7 +17869,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -17917,7 +17922,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>12</v>
       </c>
@@ -17970,7 +17975,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>5</v>
       </c>
@@ -18023,7 +18028,7 @@
         <v>102.5</v>
       </c>
     </row>
-    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>6</v>
       </c>
@@ -18076,7 +18081,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>7</v>
       </c>
@@ -18129,7 +18134,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>8</v>
       </c>
@@ -18182,7 +18187,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>9</v>
       </c>
@@ -18235,7 +18240,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>10</v>
       </c>
@@ -18288,7 +18293,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>11</v>
       </c>
@@ -18341,7 +18346,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>12</v>
       </c>
@@ -18394,7 +18399,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>5</v>
       </c>
@@ -18447,7 +18452,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>6</v>
       </c>
@@ -18500,7 +18505,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>7</v>
       </c>
@@ -18553,7 +18558,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>8</v>
       </c>
@@ -18606,7 +18611,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>9</v>
       </c>
@@ -18659,7 +18664,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
@@ -18712,7 +18717,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
@@ -18765,7 +18770,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>12</v>
       </c>
@@ -18818,7 +18823,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>5</v>
       </c>
@@ -18871,7 +18876,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>6</v>
       </c>
@@ -18924,7 +18929,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>7</v>
       </c>
@@ -18977,7 +18982,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>8</v>
       </c>
@@ -19030,7 +19035,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>9</v>
       </c>
@@ -19083,7 +19088,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>10</v>
       </c>
@@ -19136,7 +19141,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -19189,7 +19194,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>12</v>
       </c>
@@ -19242,7 +19247,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>5</v>
       </c>
@@ -19295,7 +19300,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>6</v>
       </c>
@@ -19348,7 +19353,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>7</v>
       </c>
@@ -19401,7 +19406,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>8</v>
       </c>
@@ -19454,7 +19459,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>9</v>
       </c>
@@ -19507,7 +19512,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>10</v>
       </c>
@@ -19560,7 +19565,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>11</v>
       </c>
@@ -19613,7 +19618,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>12</v>
       </c>
@@ -19666,7 +19671,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>5</v>
       </c>
@@ -19719,7 +19724,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>6</v>
       </c>
@@ -19772,7 +19777,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>7</v>
       </c>
@@ -19825,7 +19830,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>8</v>
       </c>
@@ -19878,7 +19883,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
@@ -19931,7 +19936,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -19984,7 +19989,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>11</v>
       </c>
@@ -20037,7 +20042,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>12</v>
       </c>
@@ -20090,7 +20095,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>5</v>
       </c>
@@ -20143,7 +20148,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>6</v>
       </c>
@@ -20196,7 +20201,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>7</v>
       </c>
@@ -20249,7 +20254,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>8</v>
       </c>
@@ -20302,7 +20307,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>9</v>
       </c>
@@ -20355,7 +20360,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>10</v>
       </c>
@@ -20408,7 +20413,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>11</v>
       </c>
@@ -20461,7 +20466,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>12</v>
       </c>
@@ -20514,7 +20519,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>5</v>
       </c>
@@ -20567,7 +20572,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>6</v>
       </c>
@@ -20620,7 +20625,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>7</v>
       </c>
@@ -20673,7 +20678,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>8</v>
       </c>
@@ -20726,7 +20731,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>9</v>
       </c>
@@ -20779,7 +20784,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
@@ -20832,7 +20837,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>11</v>
       </c>
@@ -20885,7 +20890,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>12</v>
       </c>
@@ -20938,7 +20943,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>5</v>
       </c>
@@ -20991,7 +20996,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>6</v>
       </c>
@@ -21044,7 +21049,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>7</v>
       </c>
@@ -21097,7 +21102,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>8</v>
       </c>
@@ -21150,7 +21155,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>9</v>
       </c>
@@ -21203,7 +21208,7 @@
         <v>182.5</v>
       </c>
     </row>
-    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>10</v>
       </c>
@@ -21256,7 +21261,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -21309,7 +21314,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>12</v>
       </c>
@@ -21362,7 +21367,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>5</v>
       </c>
@@ -21415,7 +21420,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>6</v>
       </c>
@@ -21468,7 +21473,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>7</v>
       </c>
@@ -21521,7 +21526,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>8</v>
       </c>
@@ -21574,7 +21579,7 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>9</v>
       </c>
@@ -21627,7 +21632,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -21680,7 +21685,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>11</v>
       </c>
@@ -21733,7 +21738,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>12</v>
       </c>
@@ -21786,7 +21791,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>26</v>
       </c>
@@ -21839,7 +21844,7 @@
         <v>257.5</v>
       </c>
     </row>
-    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>26</v>
       </c>
@@ -21892,7 +21897,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>26</v>
       </c>
@@ -21945,7 +21950,7 @@
         <v>322.5</v>
       </c>
     </row>
-    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>26</v>
       </c>
@@ -21998,7 +22003,7 @@
         <v>337.5</v>
       </c>
     </row>
-    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>26</v>
       </c>
@@ -22051,7 +22056,7 @@
         <v>257.5</v>
       </c>
     </row>
-    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>26</v>
       </c>
@@ -22104,7 +22109,7 @@
         <v>292.5</v>
       </c>
     </row>
-    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>26</v>
       </c>
@@ -22157,7 +22162,7 @@
         <v>292.5</v>
       </c>
     </row>
-    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>26</v>
       </c>
@@ -22210,7 +22215,7 @@
         <v>307.5</v>
       </c>
     </row>
-    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>26</v>
       </c>
@@ -22263,7 +22268,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>26</v>
       </c>
@@ -22316,7 +22321,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>26</v>
       </c>
@@ -22369,7 +22374,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>26</v>
       </c>
@@ -22422,7 +22427,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>26</v>
       </c>
@@ -22475,7 +22480,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>26</v>
       </c>
@@ -22528,7 +22533,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>26</v>
       </c>
@@ -22581,7 +22586,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>26</v>
       </c>
@@ -22634,7 +22639,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>26</v>
       </c>
@@ -22687,7 +22692,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>26</v>
       </c>
@@ -22740,7 +22745,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>26</v>
       </c>
@@ -22793,7 +22798,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>26</v>
       </c>
@@ -22847,18 +22852,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q181" xr:uid="{E3552810-31BB-4B88-9769-989F9422D843}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="24-39"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Raw"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Q181" xr:uid="{E3552810-31BB-4B88-9769-989F9422D843}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>